--- a/data/merged/2026-10-08/MERGED_UK_Spot-Cleaner_2026-10-08.xlsx
+++ b/data/merged/2026-10-08/MERGED_UK_Spot-Cleaner_2026-10-08.xlsx
@@ -5974,13 +5974,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6633,13 +6633,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>43</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6677,13 +6677,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6765,13 +6765,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>47</xdr:row>
       <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6789,94 +6789,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId45" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="46" name="Product 46">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId46" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="Product 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId47" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -7218,7 +7130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -13565,40 +13477,40 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B0GGB1CT2G</t>
         </is>
       </c>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
       <c r="F28" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="G28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0FNX6YLCJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB1CT2G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Dual-Formula Refill Cartridge, 2 x 500ml XSKBDHXCM500UKsValue 2-Pack, Formulated to tackle tough stains an</t>
+          <t>Olvy Carpet Cleaner Upholstery Spot Washer Deep Stain Removals10 Piece Kit | Pro 1650W Steam | Sofa &amp; Auto Valeting | 100°C</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B0GGB1CT2G</t>
         </is>
       </c>
       <c r="M28" s="14" t="inlineStr">
@@ -13612,13 +13524,13 @@
         </is>
       </c>
       <c r="O28" s="15">
-        <v>1938</v>
+        <v>15622</v>
       </c>
       <c r="P28" s="15">
-        <v>134</v>
+        <v>-295</v>
       </c>
       <c r="Q28" s="16">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R28" s="17" t="inlineStr">
         <is>
@@ -13627,89 +13539,101 @@
       </c>
       <c r="S28" s="18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>29</t>
         </is>
       </c>
       <c r="T28" s="15">
-        <v>1504</v>
+        <v>411</v>
       </c>
       <c r="U28" s="16">
-        <v>0.68</v>
+        <v>1.19</v>
       </c>
       <c r="V28" s="15">
-        <v>30065</v>
+        <v>27944</v>
       </c>
       <c r="W28" s="15" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>300</t>
         </is>
       </c>
       <c r="X28" s="15">
-        <v>19990</v>
+        <v>21594</v>
       </c>
       <c r="Y28" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z28" s="20">
-        <v>19.99</v>
+        <v>67.99</v>
       </c>
       <c r="AA28"/>
       <c r="AB28"/>
       <c r="AC28" s="2"/>
       <c r="AD28" s="19">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="AE28" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AF28" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG28" s="22">
-        <v>0.0053</v>
+        <v>0.0292</v>
       </c>
       <c r="AH28" s="20">
-        <v>3.1</v>
+        <v>5.94</v>
       </c>
       <c r="AI28" s="16">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="AJ28"/>
       <c r="AK28" s="13" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="AL28" s="19">
-        <v>394</v>
+        <v>268</v>
       </c>
       <c r="AM28" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN28" s="13"/>
       <c r="AO28" s="13"/>
       <c r="AP28"/>
       <c r="AQ28" s="19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR28" s="19">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AS28" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Olvy</t>
         </is>
       </c>
       <c r="AT28" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU28" s="13"/>
-      <c r="AV28" s="14"/>
-      <c r="AW28" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU28" s="13" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="AV28" s="14" t="inlineStr">
+        <is>
+          <t>NIJMEGEN Gelderland 6511DX NL</t>
+        </is>
+      </c>
+      <c r="AW28" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
+        </is>
+      </c>
       <c r="AX28" s="13"/>
       <c r="AY28" s="13" t="inlineStr">
         <is>
@@ -13719,11 +13643,7 @@
       <c r="AZ28" s="13"/>
       <c r="BA28" s="13"/>
       <c r="BB28" s="13"/>
-      <c r="BC28" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC28" s="13"/>
       <c r="BD28" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13740,47 +13660,47 @@
       </c>
       <c r="BJ28" s="23" t="inlineStr">
         <is>
-          <t>1.3 kg</t>
+          <t>3.3 kg</t>
         </is>
       </c>
       <c r="BK28" s="23" t="inlineStr">
         <is>
-          <t>1.30 kg</t>
+          <t>3.30 kg</t>
         </is>
       </c>
       <c r="BL28" s="23" t="inlineStr">
         <is>
-          <t>15.7 x 15.5 x 10.8 cm</t>
+          <t>40 x 26 x 32 cm</t>
         </is>
       </c>
       <c r="BM28" s="23" t="inlineStr">
         <is>
-          <t>15.70 x 15.50 x 10.80 cm</t>
+          <t>40.00 x 26.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BN28" s="23" t="inlineStr">
         <is>
-          <t>1.34 kg</t>
+          <t>6.7 kg</t>
         </is>
       </c>
       <c r="BO28" s="23" t="inlineStr">
         <is>
-          <t>1.34 kg</t>
+          <t>6.70 kg</t>
         </is>
       </c>
       <c r="BP28" s="23" t="inlineStr">
         <is>
-          <t>16.3 x 15.5 x 11.2 cm</t>
+          <t>42 x 39.2 x 30.5 cm</t>
         </is>
       </c>
       <c r="BQ28" s="23" t="inlineStr">
         <is>
-          <t>16.30 x 15.50 x 11.20 cm</t>
+          <t>42.00 x 39.20 x 30.50 cm</t>
         </is>
       </c>
       <c r="BR28" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -13791,40 +13711,40 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0GGB1CT2G</t>
+          <t>B00S9ORHDW</t>
         </is>
       </c>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>BISSELL</t>
         </is>
       </c>
       <c r="G29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB1CT2G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B00S9ORHDW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Olvy Carpet Cleaner Upholstery Spot Washer Deep Stain Removals10 Piece Kit | Pro 1650W Steam | Sofa &amp; Auto Valeting | 100°C</t>
+          <t>BISSELL Wash &amp; Remove Deep Clean + Oxy Formula 1.5L 1265EsFor Upright Carpet Cleaners, provides permanent stain removal</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B00S9ORHDW?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/618YXP+nVcL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0GGB1CT2G</t>
+          <t>B00S9ORHDW</t>
         </is>
       </c>
       <c r="M29" s="14" t="inlineStr">
@@ -13838,80 +13758,84 @@
         </is>
       </c>
       <c r="O29" s="15">
-        <v>15622</v>
+        <v>2455</v>
       </c>
       <c r="P29" s="15">
-        <v>-295</v>
+        <v>-490</v>
       </c>
       <c r="Q29" s="16">
-        <v>-0.02</v>
+        <v>-0.21</v>
       </c>
       <c r="R29" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers</t>
+          <t>Carpet Washers
+Carpet Cleaners</t>
         </is>
       </c>
       <c r="S29" s="18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>16
+22</t>
         </is>
       </c>
       <c r="T29" s="15">
-        <v>411</v>
+        <v>1392</v>
       </c>
       <c r="U29" s="16">
-        <v>1.19</v>
+        <v>-0.09</v>
       </c>
       <c r="V29" s="15">
-        <v>27944</v>
+        <v>27826</v>
       </c>
       <c r="W29" s="15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="X29" s="15">
-        <v>21594</v>
+        <v>19710</v>
       </c>
       <c r="Y29" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z29" s="20">
-        <v>67.99</v>
+        <v>19.99</v>
       </c>
       <c r="AA29"/>
       <c r="AB29"/>
-      <c r="AC29" s="2"/>
+      <c r="AC29" s="2">
+        <v>23</v>
+      </c>
       <c r="AD29" s="19">
-        <v>45</v>
+        <v>3397</v>
       </c>
       <c r="AE29" s="15">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="AF29" s="21">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AG29" s="22">
-        <v>0.0292</v>
+        <v>0.013600000000000001</v>
       </c>
       <c r="AH29" s="20">
-        <v>5.94</v>
+        <v>3.3</v>
       </c>
       <c r="AI29" s="16">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AJ29"/>
       <c r="AK29" s="13" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2015-07-02</t>
         </is>
       </c>
       <c r="AL29" s="19">
-        <v>268</v>
+        <v>4115</v>
       </c>
       <c r="AM29" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN29" s="13"/>
@@ -13925,39 +13849,31 @@
       </c>
       <c r="AS29" s="14" t="inlineStr">
         <is>
-          <t>Olvy</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT29" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU29" s="13" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="AV29" s="14" t="inlineStr">
-        <is>
-          <t>NIJMEGEN Gelderland 6511DX NL</t>
-        </is>
-      </c>
-      <c r="AW29" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G</t>
-        </is>
-      </c>
-      <c r="AX29" s="13"/>
-      <c r="AY29" s="13" t="inlineStr">
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU29" s="13"/>
+      <c r="AV29" s="14"/>
+      <c r="AW29" s="13"/>
+      <c r="AX29" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
+      <c r="AY29" s="13"/>
       <c r="AZ29" s="13"/>
       <c r="BA29" s="13"/>
       <c r="BB29" s="13"/>
-      <c r="BC29" s="13"/>
+      <c r="BC29" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD29" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -13967,54 +13883,50 @@
       <c r="BF29" s="13"/>
       <c r="BG29" s="13"/>
       <c r="BH29" s="14"/>
-      <c r="BI29" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI29" s="23"/>
       <c r="BJ29" s="23" t="inlineStr">
         <is>
-          <t>3.3 kg</t>
+          <t>1.65 kg</t>
         </is>
       </c>
       <c r="BK29" s="23" t="inlineStr">
         <is>
-          <t>3.30 kg</t>
+          <t>1.65 kg</t>
         </is>
       </c>
       <c r="BL29" s="23" t="inlineStr">
         <is>
-          <t>40 x 26 x 32 cm</t>
+          <t>27 x 15.5 x 8.4 cm</t>
         </is>
       </c>
       <c r="BM29" s="23" t="inlineStr">
         <is>
-          <t>40.00 x 26.00 x 32.00 cm</t>
+          <t>27.00 x 15.50 x 8.40 cm</t>
         </is>
       </c>
       <c r="BN29" s="23" t="inlineStr">
         <is>
-          <t>6.7 kg</t>
+          <t>1.65 kg</t>
         </is>
       </c>
       <c r="BO29" s="23" t="inlineStr">
         <is>
-          <t>6.70 kg</t>
+          <t>1.65 kg</t>
         </is>
       </c>
       <c r="BP29" s="23" t="inlineStr">
         <is>
-          <t>42 x 39.2 x 30.5 cm</t>
+          <t>27.1 x 15.3 x 8.2 cm</t>
         </is>
       </c>
       <c r="BQ29" s="23" t="inlineStr">
         <is>
-          <t>42.00 x 39.20 x 30.50 cm</t>
+          <t>27.10 x 15.30 x 8.20 cm</t>
         </is>
       </c>
       <c r="BR29" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>小包裹</t>
         </is>
       </c>
     </row>
@@ -14025,40 +13937,40 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B00S9ORHDW</t>
+          <t>B0DD49XPMY</t>
         </is>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B00S9ORHDW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0DD49XPMY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Wash &amp; Remove Deep Clean + Oxy Formula 1.5L 1265EsFor Upright Carpet Cleaners, provides permanent stain removal</t>
+          <t>Shark StainStriker HairPro Pet Spot Cleaner, Carpet &amp; Upholstory CleanersAnti-Clog Pet Hair Extractor, Removes Tough Stains</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B00S9ORHDW?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/618YXP+nVcL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B00S9ORHDW</t>
+          <t>B0DD49XPMY</t>
         </is>
       </c>
       <c r="M30" s="14" t="inlineStr">
@@ -14072,80 +13984,76 @@
         </is>
       </c>
       <c r="O30" s="15">
-        <v>2455</v>
+        <v>28863</v>
       </c>
       <c r="P30" s="15">
-        <v>-490</v>
+        <v>-5095</v>
       </c>
       <c r="Q30" s="16">
         <v>-0.21</v>
       </c>
       <c r="R30" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers
-Carpet Cleaners</t>
+          <t>Carpet Washers</t>
         </is>
       </c>
       <c r="S30" s="18" t="inlineStr">
         <is>
-          <t>16
-22</t>
+          <t>33</t>
         </is>
       </c>
       <c r="T30" s="15">
-        <v>1392</v>
+        <v>169</v>
       </c>
       <c r="U30" s="16">
-        <v>-0.09</v>
+        <v>0.26</v>
       </c>
       <c r="V30" s="15">
-        <v>27826</v>
+        <v>25181</v>
       </c>
       <c r="W30" s="15" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X30" s="15">
-        <v>19710</v>
+        <v>16365</v>
       </c>
       <c r="Y30" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z30" s="20">
-        <v>19.99</v>
+        <v>149</v>
       </c>
       <c r="AA30"/>
       <c r="AB30"/>
-      <c r="AC30" s="2">
-        <v>23</v>
-      </c>
+      <c r="AC30" s="2"/>
       <c r="AD30" s="19">
-        <v>3397</v>
+        <v>195</v>
       </c>
       <c r="AE30" s="15">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="AF30" s="21">
         <v>4.6</v>
       </c>
       <c r="AG30" s="22">
-        <v>0.013600000000000001</v>
+        <v>0.023700000000000002</v>
       </c>
       <c r="AH30" s="20">
-        <v>3.3</v>
+        <v>5.63</v>
       </c>
       <c r="AI30" s="16">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="AJ30"/>
       <c r="AK30" s="13" t="inlineStr">
         <is>
-          <t>2015-07-02</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AL30" s="19">
-        <v>4115</v>
+        <v>761</v>
       </c>
       <c r="AM30" s="13" t="inlineStr">
         <is>
@@ -14156,10 +14064,10 @@
       <c r="AO30" s="13"/>
       <c r="AP30"/>
       <c r="AQ30" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR30" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS30" s="14" t="inlineStr">
         <is>
@@ -14174,12 +14082,12 @@
       <c r="AU30" s="13"/>
       <c r="AV30" s="14"/>
       <c r="AW30" s="13"/>
-      <c r="AX30" s="13" t="inlineStr">
+      <c r="AX30" s="13"/>
+      <c r="AY30" s="13" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="AY30" s="13"/>
       <c r="AZ30" s="13"/>
       <c r="BA30" s="13"/>
       <c r="BB30" s="13"/>
@@ -14197,50 +14105,54 @@
       <c r="BF30" s="13"/>
       <c r="BG30" s="13"/>
       <c r="BH30" s="14"/>
-      <c r="BI30" s="23"/>
+      <c r="BI30" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ30" s="23" t="inlineStr">
         <is>
-          <t>1.65 kg</t>
+          <t>3.5 kg</t>
         </is>
       </c>
       <c r="BK30" s="23" t="inlineStr">
         <is>
-          <t>1.65 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL30" s="23" t="inlineStr">
         <is>
-          <t>27 x 15.5 x 8.4 cm</t>
+          <t>34.3 x 30.2 x 38 cm</t>
         </is>
       </c>
       <c r="BM30" s="23" t="inlineStr">
         <is>
-          <t>27.00 x 15.50 x 8.40 cm</t>
+          <t>34.30 x 30.20 x 38.00 cm</t>
         </is>
       </c>
       <c r="BN30" s="23" t="inlineStr">
         <is>
-          <t>1.65 kg</t>
+          <t>6.8 kg</t>
         </is>
       </c>
       <c r="BO30" s="23" t="inlineStr">
         <is>
-          <t>1.65 kg</t>
+          <t>6.80 kg</t>
         </is>
       </c>
       <c r="BP30" s="23" t="inlineStr">
         <is>
-          <t>27.1 x 15.3 x 8.2 cm</t>
+          <t>39.4 x 35.6 x 31 cm</t>
         </is>
       </c>
       <c r="BQ30" s="23" t="inlineStr">
         <is>
-          <t>27.10 x 15.30 x 8.20 cm</t>
+          <t>39.40 x 35.60 x 31.00 cm</t>
         </is>
       </c>
       <c r="BR30" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14251,40 +14163,40 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0DD49XPMY</t>
+          <t>B0DSZVCZ6P</t>
         </is>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>Hjh</t>
         </is>
       </c>
       <c r="G31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0DD49XPMY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker HairPro Pet Spot Cleaner, Carpet &amp; Upholstory CleanersAnti-Clog Pet Hair Extractor, Removes Tough Stains</t>
+          <t>Carpet Cleaner &amp; Spot Cleaner, Handheld Carpet Cleaner MachinessUpholstery Cleaner | Clean Up Spills &amp; Pet Messes from Carp</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0DD49XPMY</t>
+          <t>B0DSZVCZ6P</t>
         </is>
       </c>
       <c r="M31" s="14" t="inlineStr">
@@ -14298,13 +14210,13 @@
         </is>
       </c>
       <c r="O31" s="15">
-        <v>28863</v>
+        <v>12096</v>
       </c>
       <c r="P31" s="15">
-        <v>-5095</v>
+        <v>2774</v>
       </c>
       <c r="Q31" s="16">
-        <v>-0.21</v>
+        <v>0.2</v>
       </c>
       <c r="R31" s="17" t="inlineStr">
         <is>
@@ -14313,89 +14225,101 @@
       </c>
       <c r="S31" s="18" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>21</t>
         </is>
       </c>
       <c r="T31" s="15">
-        <v>169</v>
+        <v>401</v>
       </c>
       <c r="U31" s="16">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="V31" s="15">
-        <v>25181</v>
+        <v>24056</v>
       </c>
       <c r="W31" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="X31" s="15">
-        <v>16365</v>
+        <v>11878</v>
       </c>
       <c r="Y31" s="19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z31" s="20">
-        <v>149</v>
+        <v>59.99</v>
       </c>
       <c r="AA31"/>
       <c r="AB31"/>
       <c r="AC31" s="2"/>
       <c r="AD31" s="19">
-        <v>195</v>
+        <v>344</v>
       </c>
       <c r="AE31" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AF31" s="21">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="AG31" s="22">
-        <v>0.023700000000000002</v>
+        <v>0.005</v>
       </c>
       <c r="AH31" s="20">
-        <v>5.63</v>
+        <v>3.43</v>
       </c>
       <c r="AI31" s="16">
-        <v>0.96</v>
+        <v>0.94</v>
       </c>
       <c r="AJ31"/>
       <c r="AK31" s="13" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="AL31" s="19">
-        <v>761</v>
+        <v>604</v>
       </c>
       <c r="AM31" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN31" s="13"/>
       <c r="AO31" s="13"/>
       <c r="AP31"/>
       <c r="AQ31" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR31" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS31" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>penmingkeji</t>
         </is>
       </c>
       <c r="AT31" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU31" s="13"/>
-      <c r="AV31" s="14"/>
-      <c r="AW31" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU31" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV31" s="14" t="inlineStr">
+        <is>
+          <t>安庆市 安徽 246000 CN</t>
+        </is>
+      </c>
+      <c r="AW31" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH</t>
+        </is>
+      </c>
       <c r="AX31" s="13"/>
       <c r="AY31" s="13" t="inlineStr">
         <is>
@@ -14426,47 +14350,47 @@
       </c>
       <c r="BJ31" s="23" t="inlineStr">
         <is>
-          <t>3.5 kg</t>
+          <t>4.3 kg</t>
         </is>
       </c>
       <c r="BK31" s="23" t="inlineStr">
         <is>
-          <t>3.50 kg</t>
+          <t>4.30 kg</t>
         </is>
       </c>
       <c r="BL31" s="23" t="inlineStr">
         <is>
-          <t>34.3 x 30.2 x 38 cm</t>
+          <t>44 x 33.9 x 19.7 cm</t>
         </is>
       </c>
       <c r="BM31" s="23" t="inlineStr">
         <is>
-          <t>34.30 x 30.20 x 38.00 cm</t>
+          <t>44.00 x 33.90 x 19.70 cm</t>
         </is>
       </c>
       <c r="BN31" s="23" t="inlineStr">
         <is>
-          <t>6.8 kg</t>
+          <t>4.74 kg</t>
         </is>
       </c>
       <c r="BO31" s="23" t="inlineStr">
         <is>
-          <t>6.80 kg</t>
+          <t>4.74 kg</t>
         </is>
       </c>
       <c r="BP31" s="23" t="inlineStr">
         <is>
-          <t>39.4 x 35.6 x 31 cm</t>
+          <t>44.8 x 33.8 x 19.2 cm</t>
         </is>
       </c>
       <c r="BQ31" s="23" t="inlineStr">
         <is>
-          <t>39.40 x 35.60 x 31.00 cm</t>
+          <t>44.80 x 33.80 x 19.20 cm</t>
         </is>
       </c>
       <c r="BR31" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -14477,40 +14401,40 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0DSZVCZ6P</t>
+          <t>B0D6RSDL6X</t>
         </is>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>Hjh</t>
+          <t>BISSELL</t>
         </is>
       </c>
       <c r="G32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh</t>
+          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0D6RSDL6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>Carpet Cleaner &amp; Spot Cleaner, Handheld Carpet Cleaner MachinessUpholstery Cleaner | Clean Up Spills &amp; Pet Messes from Carp</t>
+          <t>BISSELL Little Green Portable Spot Cleaner &amp; Carpet Stain Remover 4098EsUpholstery and sofa cleaner with powerful suction,</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0DSZVCZ6P</t>
+          <t>B0D6RSDL6X</t>
         </is>
       </c>
       <c r="M32" s="14" t="inlineStr">
@@ -14524,13 +14448,13 @@
         </is>
       </c>
       <c r="O32" s="15">
-        <v>12096</v>
+        <v>4261</v>
       </c>
       <c r="P32" s="15">
-        <v>2774</v>
+        <v>26103</v>
       </c>
       <c r="Q32" s="16">
-        <v>0.2</v>
+        <v>0.86</v>
       </c>
       <c r="R32" s="17" t="inlineStr">
         <is>
@@ -14539,17 +14463,17 @@
       </c>
       <c r="S32" s="18" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="T32" s="15">
-        <v>401</v>
+        <v>270</v>
       </c>
       <c r="U32" s="16">
-        <v>0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="V32" s="15">
-        <v>24056</v>
+        <v>22137</v>
       </c>
       <c r="W32" s="15" t="inlineStr">
         <is>
@@ -14557,83 +14481,71 @@
         </is>
       </c>
       <c r="X32" s="15">
-        <v>11878</v>
+        <v>23720</v>
       </c>
       <c r="Y32" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z32" s="20">
-        <v>59.99</v>
+        <v>89.99</v>
       </c>
       <c r="AA32"/>
       <c r="AB32"/>
       <c r="AC32" s="2"/>
       <c r="AD32" s="19">
-        <v>344</v>
+        <v>293</v>
       </c>
       <c r="AE32" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF32" s="21">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AG32" s="22">
-        <v>0.005</v>
+        <v>0.0037</v>
       </c>
       <c r="AH32" s="20">
-        <v>3.43</v>
+        <v>5.48</v>
       </c>
       <c r="AI32" s="16">
-        <v>0.94</v>
+        <v>0.93</v>
       </c>
       <c r="AJ32"/>
       <c r="AK32" s="13" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AL32" s="19">
-        <v>604</v>
+        <v>848</v>
       </c>
       <c r="AM32" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN32" s="13"/>
       <c r="AO32" s="13"/>
       <c r="AP32"/>
       <c r="AQ32" s="19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR32" s="19">
         <v>1</v>
       </c>
       <c r="AS32" s="14" t="inlineStr">
         <is>
-          <t>penmingkeji</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT32" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU32" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV32" s="14" t="inlineStr">
-        <is>
-          <t>安庆市 安徽 246000 CN</t>
-        </is>
-      </c>
-      <c r="AW32" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU32" s="13"/>
+      <c r="AV32" s="14"/>
+      <c r="AW32" s="13"/>
       <c r="AX32" s="13"/>
       <c r="AY32" s="13" t="inlineStr">
         <is>
@@ -14664,47 +14576,47 @@
       </c>
       <c r="BJ32" s="23" t="inlineStr">
         <is>
-          <t>4.3 kg</t>
+          <t>4.38 kg</t>
         </is>
       </c>
       <c r="BK32" s="23" t="inlineStr">
         <is>
-          <t>4.30 kg</t>
+          <t>4.38 kg</t>
         </is>
       </c>
       <c r="BL32" s="23" t="inlineStr">
         <is>
-          <t>44 x 33.9 x 19.7 cm</t>
+          <t>21 x 44 x 31.8 cm</t>
         </is>
       </c>
       <c r="BM32" s="23" t="inlineStr">
         <is>
-          <t>44.00 x 33.90 x 19.70 cm</t>
+          <t>21.00 x 44.00 x 31.80 cm</t>
         </is>
       </c>
       <c r="BN32" s="23" t="inlineStr">
         <is>
-          <t>4.74 kg</t>
+          <t>6.24 kg</t>
         </is>
       </c>
       <c r="BO32" s="23" t="inlineStr">
         <is>
-          <t>4.74 kg</t>
+          <t>6.24 kg</t>
         </is>
       </c>
       <c r="BP32" s="23" t="inlineStr">
         <is>
-          <t>44.8 x 33.8 x 19.2 cm</t>
+          <t>46.5 x 34.7 x 23.5 cm</t>
         </is>
       </c>
       <c r="BQ32" s="23" t="inlineStr">
         <is>
-          <t>44.80 x 33.80 x 19.20 cm</t>
+          <t>46.50 x 34.70 x 23.50 cm</t>
         </is>
       </c>
       <c r="BR32" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -14715,40 +14627,40 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0D6RSDL6X</t>
+          <t>B00T31O22Y</t>
         </is>
       </c>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Rug Doctor</t>
         </is>
       </c>
       <c r="G33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0D6RSDL6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Portable Spot Cleaner &amp; Carpet Stain Remover 4098EsUpholstery and sofa cleaner with powerful suction,</t>
+          <t>Rug Doctor Portable Spot Cleaner (1100W)sThe Telegraph’s 2025 “Best Buy” - 2X Suction - Motorised Brush - Handheld Tools fo</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B00T31O22Y?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41z1m5EzSeL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0D6RSDL6X</t>
+          <t>B00T31O22Y</t>
         </is>
       </c>
       <c r="M33" s="14" t="inlineStr">
@@ -14762,13 +14674,13 @@
         </is>
       </c>
       <c r="O33" s="15">
-        <v>4261</v>
+        <v>87320</v>
       </c>
       <c r="P33" s="15">
-        <v>26103</v>
+        <v>11531</v>
       </c>
       <c r="Q33" s="16">
-        <v>0.86</v>
+        <v>0.27</v>
       </c>
       <c r="R33" s="17" t="inlineStr">
         <is>
@@ -14777,61 +14689,57 @@
       </c>
       <c r="S33" s="18" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>70</t>
         </is>
       </c>
       <c r="T33" s="15">
-        <v>270</v>
+        <v>157</v>
       </c>
       <c r="U33" s="16">
-        <v>-0.15</v>
+        <v>-0.63</v>
       </c>
       <c r="V33" s="15">
-        <v>22137</v>
-      </c>
-      <c r="W33" s="15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="X33" s="15">
-        <v>23720</v>
-      </c>
+        <v>19887</v>
+      </c>
+      <c r="W33" s="15"/>
+      <c r="X33" s="15"/>
       <c r="Y33" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z33" s="20">
-        <v>89.99</v>
+        <v>167.85</v>
       </c>
       <c r="AA33"/>
       <c r="AB33"/>
-      <c r="AC33" s="2"/>
+      <c r="AC33" s="2">
+        <v>82</v>
+      </c>
       <c r="AD33" s="19">
-        <v>293</v>
+        <v>3750</v>
       </c>
       <c r="AE33" s="15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF33" s="21">
         <v>4.4</v>
       </c>
       <c r="AG33" s="22">
-        <v>0.0037</v>
+        <v>0</v>
       </c>
       <c r="AH33" s="20">
-        <v>5.48</v>
+        <v>6.39</v>
       </c>
       <c r="AI33" s="16">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="AJ33"/>
       <c r="AK33" s="13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2015-02-10</t>
         </is>
       </c>
       <c r="AL33" s="19">
-        <v>848</v>
+        <v>4258</v>
       </c>
       <c r="AM33" s="13" t="inlineStr">
         <is>
@@ -14890,42 +14798,42 @@
       </c>
       <c r="BJ33" s="23" t="inlineStr">
         <is>
-          <t>4.38 kg</t>
+          <t>7.45 Kilograms</t>
         </is>
       </c>
       <c r="BK33" s="23" t="inlineStr">
         <is>
-          <t>4.38 kg</t>
+          <t>7.45 kg</t>
         </is>
       </c>
       <c r="BL33" s="23" t="inlineStr">
         <is>
-          <t>21 x 44 x 31.8 cm</t>
+          <t>41 x 28 x 40 cm</t>
         </is>
       </c>
       <c r="BM33" s="23" t="inlineStr">
         <is>
-          <t>21.00 x 44.00 x 31.80 cm</t>
+          <t>41.00 x 28.00 x 40.00 cm</t>
         </is>
       </c>
       <c r="BN33" s="23" t="inlineStr">
         <is>
-          <t>6.24 kg</t>
+          <t>9.05 kg</t>
         </is>
       </c>
       <c r="BO33" s="23" t="inlineStr">
         <is>
-          <t>6.24 kg</t>
+          <t>9.05 kg</t>
         </is>
       </c>
       <c r="BP33" s="23" t="inlineStr">
         <is>
-          <t>46.5 x 34.7 x 23.5 cm</t>
+          <t>45.2 x 44.6 x 32.2 cm</t>
         </is>
       </c>
       <c r="BQ33" s="23" t="inlineStr">
         <is>
-          <t>46.50 x 34.70 x 23.50 cm</t>
+          <t>45.20 x 44.60 x 32.20 cm</t>
         </is>
       </c>
       <c r="BR33" s="13" t="inlineStr">
@@ -14941,40 +14849,40 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B00T31O22Y</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor</t>
+          <t>Beldray</t>
         </is>
       </c>
       <c r="G34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor Portable Spot Cleaner (1100W)sThe Telegraph’s 2025 “Best Buy” - 2X Suction - Motorised Brush - Handheld Tools fo</t>
+          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B00T31O22Y?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41z1m5EzSeL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B00T31O22Y</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="M34" s="14" t="inlineStr">
@@ -14988,13 +14896,13 @@
         </is>
       </c>
       <c r="O34" s="15">
-        <v>87320</v>
+        <v>33464</v>
       </c>
       <c r="P34" s="15">
-        <v>11531</v>
+        <v>-16420</v>
       </c>
       <c r="Q34" s="16">
-        <v>0.27</v>
+        <v>-0.96</v>
       </c>
       <c r="R34" s="17" t="inlineStr">
         <is>
@@ -15003,61 +14911,65 @@
       </c>
       <c r="S34" s="18" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T34" s="15">
-        <v>157</v>
+        <v>272</v>
       </c>
       <c r="U34" s="16">
-        <v>-0.63</v>
+        <v>0.45</v>
       </c>
       <c r="V34" s="15">
-        <v>19887</v>
-      </c>
-      <c r="W34" s="15"/>
-      <c r="X34" s="15"/>
+        <v>14957</v>
+      </c>
+      <c r="W34" s="15" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="X34" s="15">
+        <v>10074</v>
+      </c>
       <c r="Y34" s="19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z34" s="20">
-        <v>167.85</v>
+        <v>54.99</v>
       </c>
       <c r="AA34"/>
       <c r="AB34"/>
-      <c r="AC34" s="2">
-        <v>82</v>
-      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" s="19">
-        <v>3750</v>
+        <v>22</v>
       </c>
       <c r="AE34" s="15">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AF34" s="21">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AG34" s="22">
-        <v>0</v>
+        <v>0.0331</v>
       </c>
       <c r="AH34" s="20">
-        <v>6.39</v>
+        <v>5.18</v>
       </c>
       <c r="AI34" s="16">
-        <v>0.94</v>
+        <v>0.91</v>
       </c>
       <c r="AJ34"/>
       <c r="AK34" s="13" t="inlineStr">
         <is>
-          <t>2015-02-10</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="AL34" s="19">
-        <v>4258</v>
+        <v>542</v>
       </c>
       <c r="AM34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN34" s="13"/>
@@ -15071,17 +14983,29 @@
       </c>
       <c r="AS34" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>homeofbrands</t>
         </is>
       </c>
       <c r="AT34" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU34" s="13"/>
-      <c r="AV34" s="14"/>
-      <c r="AW34" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU34" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV34" s="14" t="inlineStr">
+        <is>
+          <t>Chadderton Oldham OL9 0DD GB</t>
+        </is>
+      </c>
+      <c r="AW34" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W</t>
+        </is>
+      </c>
       <c r="AX34" s="13"/>
       <c r="AY34" s="13" t="inlineStr">
         <is>
@@ -15112,42 +15036,42 @@
       </c>
       <c r="BJ34" s="23" t="inlineStr">
         <is>
-          <t>7.45 Kilograms</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK34" s="23" t="inlineStr">
         <is>
-          <t>7.45 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL34" s="23" t="inlineStr">
         <is>
-          <t>41 x 28 x 40 cm</t>
+          <t>26 x 22 x 27 cm</t>
         </is>
       </c>
       <c r="BM34" s="23" t="inlineStr">
         <is>
-          <t>41.00 x 28.00 x 40.00 cm</t>
+          <t>26.00 x 22.00 x 27.00 cm</t>
         </is>
       </c>
       <c r="BN34" s="23" t="inlineStr">
         <is>
-          <t>9.05 kg</t>
+          <t>3.56 kg</t>
         </is>
       </c>
       <c r="BO34" s="23" t="inlineStr">
         <is>
-          <t>9.05 kg</t>
+          <t>3.56 kg</t>
         </is>
       </c>
       <c r="BP34" s="23" t="inlineStr">
         <is>
-          <t>45.2 x 44.6 x 32.2 cm</t>
+          <t>36.3 x 35 x 21.6 cm</t>
         </is>
       </c>
       <c r="BQ34" s="23" t="inlineStr">
         <is>
-          <t>45.20 x 44.60 x 32.20 cm</t>
+          <t>36.30 x 35.00 x 21.60 cm</t>
         </is>
       </c>
       <c r="BR34" s="13" t="inlineStr">
@@ -15163,40 +15087,40 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0HJ8J22N9</t>
         </is>
       </c>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>Beldray</t>
+          <t>VonHaus</t>
         </is>
       </c>
       <c r="G35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
+          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0HJ8J22N9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
+          <t>Vonhaus Spot Cleaner 450W, Ultra Lightweight Handheld Carpet Cleaner 2.6kgs1L Carpet Washer &amp; Sofa Cleaner Machine with Dua</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HJ8J22N9?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41CYhsHx-oL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0HJ8J22N9</t>
         </is>
       </c>
       <c r="M35" s="14" t="inlineStr">
@@ -15210,13 +15134,13 @@
         </is>
       </c>
       <c r="O35" s="15">
-        <v>33464</v>
+        <v>18664</v>
       </c>
       <c r="P35" s="15">
-        <v>-16420</v>
+        <v>3085</v>
       </c>
       <c r="Q35" s="16">
-        <v>-0.96</v>
+        <v>0.14</v>
       </c>
       <c r="R35" s="17" t="inlineStr">
         <is>
@@ -15225,28 +15149,22 @@
       </c>
       <c r="S35" s="18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T35" s="15">
-        <v>272</v>
+        <v>238</v>
       </c>
       <c r="U35" s="16">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="V35" s="15">
-        <v>14957</v>
-      </c>
-      <c r="W35" s="15" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="X35" s="15">
-        <v>10074</v>
-      </c>
+        <v>13088</v>
+      </c>
+      <c r="W35" s="15"/>
+      <c r="X35" s="15"/>
       <c r="Y35" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z35" s="20">
         <v>54.99</v>
@@ -15255,31 +15173,31 @@
       <c r="AB35"/>
       <c r="AC35" s="2"/>
       <c r="AD35" s="19">
-        <v>22</v>
+        <v>70</v>
       </c>
       <c r="AE35" s="15">
         <v>9</v>
       </c>
       <c r="AF35" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG35" s="22">
-        <v>0.0331</v>
+        <v>0.0378</v>
       </c>
       <c r="AH35" s="20">
-        <v>5.18</v>
+        <v>3.59</v>
       </c>
       <c r="AI35" s="16">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="AJ35"/>
       <c r="AK35" s="13" t="inlineStr">
         <is>
-          <t>2025-04-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AL35" s="19">
-        <v>542</v>
+        <v>28</v>
       </c>
       <c r="AM35" s="13" t="inlineStr">
         <is>
@@ -15290,14 +15208,14 @@
       <c r="AO35" s="13"/>
       <c r="AP35"/>
       <c r="AQ35" s="19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AR35" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS35" s="14" t="inlineStr">
         <is>
-          <t>homeofbrands</t>
+          <t>VonHaus UK</t>
         </is>
       </c>
       <c r="AT35" s="13" t="inlineStr">
@@ -15312,12 +15230,12 @@
       </c>
       <c r="AV35" s="14" t="inlineStr">
         <is>
-          <t>Chadderton Oldham OL9 0DD GB</t>
+          <t>SALFORD M3 7BF GB</t>
         </is>
       </c>
       <c r="AW35" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
         </is>
       </c>
       <c r="AX35" s="13"/>
@@ -15334,11 +15252,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD35" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD35" s="13"/>
       <c r="BE35" s="13"/>
       <c r="BF35" s="13"/>
       <c r="BG35" s="13"/>
@@ -15350,47 +15264,43 @@
       </c>
       <c r="BJ35" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>2.6 Kilograms</t>
         </is>
       </c>
       <c r="BK35" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
+          <t>2.60 kg</t>
         </is>
       </c>
       <c r="BL35" s="23" t="inlineStr">
         <is>
-          <t>26 x 22 x 27 cm</t>
-        </is>
-      </c>
-      <c r="BM35" s="23" t="inlineStr">
-        <is>
-          <t>26.00 x 22.00 x 27.00 cm</t>
-        </is>
-      </c>
+          <t>17.1D x 25.7W x 27.2H centimetres</t>
+        </is>
+      </c>
+      <c r="BM35" s="23"/>
       <c r="BN35" s="23" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>3.57 kg</t>
         </is>
       </c>
       <c r="BO35" s="23" t="inlineStr">
         <is>
-          <t>3.56 kg</t>
+          <t>3.57 kg</t>
         </is>
       </c>
       <c r="BP35" s="23" t="inlineStr">
         <is>
-          <t>36.3 x 35 x 21.6 cm</t>
+          <t>36.3 x 31.3 x 16.4 cm</t>
         </is>
       </c>
       <c r="BQ35" s="23" t="inlineStr">
         <is>
-          <t>36.30 x 35.00 x 21.60 cm</t>
+          <t>36.30 x 31.30 x 16.40 cm</t>
         </is>
       </c>
       <c r="BR35" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -15401,40 +15311,40 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0HJ8J22N9</t>
+          <t>B0FP2ZHPNR</t>
         </is>
       </c>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>VonHaus</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0HJ8J22N9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FP2ZHPNR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>Vonhaus Spot Cleaner 450W, Ultra Lightweight Handheld Carpet Cleaner 2.6kgs1L Carpet Washer &amp; Sofa Cleaner Machine with Dua</t>
+          <t>Kärcher SE 2 Spot Care Spot Cleaner, 1.5 l Fresh Water TanksPower consumption: 450 W, area: 2.89 m², weight: 4.2 kg, spray</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0HJ8J22N9?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41CYhsHx-oL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41gGVJL+XcL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0HJ8J22N9</t>
+          <t>B0FP2ZHPNR</t>
         </is>
       </c>
       <c r="M36" s="14" t="inlineStr">
@@ -15448,13 +15358,13 @@
         </is>
       </c>
       <c r="O36" s="15">
-        <v>18664</v>
+        <v>35947</v>
       </c>
       <c r="P36" s="15">
-        <v>3085</v>
+        <v>-4971</v>
       </c>
       <c r="Q36" s="16">
-        <v>0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="R36" s="17" t="inlineStr">
         <is>
@@ -15463,95 +15373,89 @@
       </c>
       <c r="S36" s="18" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T36" s="15">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="U36" s="16">
-        <v>0.52</v>
+        <v>-0.32</v>
       </c>
       <c r="V36" s="15">
-        <v>13088</v>
-      </c>
-      <c r="W36" s="15"/>
-      <c r="X36" s="15"/>
+        <v>13018</v>
+      </c>
+      <c r="W36" s="15" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="X36" s="15">
+        <v>9780</v>
+      </c>
       <c r="Y36" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" s="20">
-        <v>54.99</v>
+        <v>98.28</v>
       </c>
       <c r="AA36"/>
       <c r="AB36"/>
       <c r="AC36" s="2"/>
       <c r="AD36" s="19">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="AE36" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AF36" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG36" s="22">
-        <v>0.0378</v>
+        <v>0.0323</v>
       </c>
       <c r="AH36" s="20">
-        <v>3.59</v>
+        <v>5.63</v>
       </c>
       <c r="AI36" s="16">
-        <v>0.93</v>
+        <v>0.94</v>
       </c>
       <c r="AJ36"/>
       <c r="AK36" s="13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-09-02</t>
         </is>
       </c>
       <c r="AL36" s="19">
-        <v>28</v>
+        <v>401</v>
       </c>
       <c r="AM36" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN36" s="13"/>
       <c r="AO36" s="13"/>
       <c r="AP36"/>
       <c r="AQ36" s="19">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AR36" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS36" s="14" t="inlineStr">
         <is>
-          <t>VonHaus UK</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT36" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU36" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV36" s="14" t="inlineStr">
-        <is>
-          <t>SALFORD M3 7BF GB</t>
-        </is>
-      </c>
-      <c r="AW36" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU36" s="13"/>
+      <c r="AV36" s="14"/>
+      <c r="AW36" s="13"/>
       <c r="AX36" s="13"/>
       <c r="AY36" s="13" t="inlineStr">
         <is>
@@ -15578,43 +15482,43 @@
       </c>
       <c r="BJ36" s="23" t="inlineStr">
         <is>
-          <t>2.6 Kilograms</t>
+          <t>4.03 Kilograms</t>
         </is>
       </c>
       <c r="BK36" s="23" t="inlineStr">
         <is>
-          <t>2.60 kg</t>
+          <t>4.03 kg</t>
         </is>
       </c>
       <c r="BL36" s="23" t="inlineStr">
         <is>
-          <t>17.1D x 25.7W x 27.2H centimetres</t>
+          <t>38.5D x 21.5W x 31H centimetres</t>
         </is>
       </c>
       <c r="BM36" s="23"/>
       <c r="BN36" s="23" t="inlineStr">
         <is>
-          <t>3.57 kg</t>
+          <t>5.77 kg</t>
         </is>
       </c>
       <c r="BO36" s="23" t="inlineStr">
         <is>
-          <t>3.57 kg</t>
+          <t>5.77 kg</t>
         </is>
       </c>
       <c r="BP36" s="23" t="inlineStr">
         <is>
-          <t>36.3 x 31.3 x 16.4 cm</t>
+          <t>44.2 x 35 x 25.9 cm</t>
         </is>
       </c>
       <c r="BQ36" s="23" t="inlineStr">
         <is>
-          <t>36.30 x 31.30 x 16.40 cm</t>
+          <t>44.20 x 35.00 x 25.90 cm</t>
         </is>
       </c>
       <c r="BR36" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -15625,40 +15529,40 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0FP2ZHPNR</t>
+          <t>B0GL3ZR1JF</t>
         </is>
       </c>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="G37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FP2ZHPNR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0GL3ZR1JF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>Kärcher SE 2 Spot Care Spot Cleaner, 1.5 l Fresh Water TanksPower consumption: 450 W, area: 2.89 m², weight: 4.2 kg, spray</t>
+          <t>Shark EveryMess 3-in-1 Stain Eliminator, Wet &amp; Dry Vac, VX110UK - PetssUltra-Powerful suction. Multi-surface versatility. P</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GL3ZR1JF?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41gGVJL+XcL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71j+wRZ7ZaL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0FP2ZHPNR</t>
+          <t>B0GL3ZR1JF</t>
         </is>
       </c>
       <c r="M37" s="14" t="inlineStr">
@@ -15672,13 +15576,13 @@
         </is>
       </c>
       <c r="O37" s="15">
-        <v>35947</v>
+        <v>16404</v>
       </c>
       <c r="P37" s="15">
-        <v>-4971</v>
+        <v>28476</v>
       </c>
       <c r="Q37" s="16">
-        <v>-0.16</v>
+        <v>0.63</v>
       </c>
       <c r="R37" s="17" t="inlineStr">
         <is>
@@ -15687,49 +15591,49 @@
       </c>
       <c r="S37" s="18" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T37" s="15">
-        <v>217</v>
+        <v>106</v>
       </c>
       <c r="U37" s="16">
-        <v>-0.32</v>
+        <v>0.84</v>
       </c>
       <c r="V37" s="15">
-        <v>13018</v>
+        <v>11378</v>
       </c>
       <c r="W37" s="15" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="X37" s="15">
-        <v>9780</v>
+        <v>6325</v>
       </c>
       <c r="Y37" s="19">
         <v>1</v>
       </c>
       <c r="Z37" s="20">
-        <v>98.28</v>
+        <v>107.34</v>
       </c>
       <c r="AA37"/>
       <c r="AB37"/>
       <c r="AC37" s="2"/>
       <c r="AD37" s="19">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="AE37" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AF37" s="21">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AG37" s="22">
-        <v>0.0323</v>
+        <v>0.028300000000000002</v>
       </c>
       <c r="AH37" s="20">
-        <v>5.63</v>
+        <v>6.09</v>
       </c>
       <c r="AI37" s="16">
         <v>0.94</v>
@@ -15737,11 +15641,11 @@
       <c r="AJ37"/>
       <c r="AK37" s="13" t="inlineStr">
         <is>
-          <t>2025-09-02</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="AL37" s="19">
-        <v>401</v>
+        <v>231</v>
       </c>
       <c r="AM37" s="13" t="inlineStr">
         <is>
@@ -15755,7 +15659,7 @@
         <v>9</v>
       </c>
       <c r="AR37" s="19">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="AS37" s="14" t="inlineStr">
         <is>
@@ -15784,7 +15688,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD37" s="13"/>
+      <c r="BD37" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE37" s="13"/>
       <c r="BF37" s="13"/>
       <c r="BG37" s="13"/>
@@ -15796,38 +15704,42 @@
       </c>
       <c r="BJ37" s="23" t="inlineStr">
         <is>
-          <t>4.03 Kilograms</t>
+          <t>4.67 kg</t>
         </is>
       </c>
       <c r="BK37" s="23" t="inlineStr">
         <is>
-          <t>4.03 kg</t>
+          <t>4.67 kg</t>
         </is>
       </c>
       <c r="BL37" s="23" t="inlineStr">
         <is>
-          <t>38.5D x 21.5W x 31H centimetres</t>
-        </is>
-      </c>
-      <c r="BM37" s="23"/>
+          <t>26.7 x 41.9 x 34.3 cm</t>
+        </is>
+      </c>
+      <c r="BM37" s="23" t="inlineStr">
+        <is>
+          <t>26.70 x 41.90 x 34.30 cm</t>
+        </is>
+      </c>
       <c r="BN37" s="23" t="inlineStr">
         <is>
-          <t>5.77 kg</t>
+          <t>7.75 kg</t>
         </is>
       </c>
       <c r="BO37" s="23" t="inlineStr">
         <is>
-          <t>5.77 kg</t>
+          <t>7.75 kg</t>
         </is>
       </c>
       <c r="BP37" s="23" t="inlineStr">
         <is>
-          <t>44.2 x 35 x 25.9 cm</t>
+          <t>53.5 x 40.5 x 26.7 cm</t>
         </is>
       </c>
       <c r="BQ37" s="23" t="inlineStr">
         <is>
-          <t>44.20 x 35.00 x 25.90 cm</t>
+          <t>53.50 x 40.50 x 26.70 cm</t>
         </is>
       </c>
       <c r="BR37" s="13" t="inlineStr">
@@ -15843,40 +15755,40 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0GL3ZR1JF</t>
+          <t>B0DPGJG95L</t>
         </is>
       </c>
       <c r="D38" s="14"/>
       <c r="E38" s="14"/>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>BISSELL</t>
         </is>
       </c>
       <c r="G38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0GL3ZR1JF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0DPGJG95L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Shark EveryMess 3-in-1 Stain Eliminator, Wet &amp; Dry Vac, VX110UK - PetssUltra-Powerful suction. Multi-surface versatility. P</t>
+          <t>BISSELL PowerWash Compact Pet Upright Carpet &amp; Upholstery Cleaner 4058EsCompact carpet washer with removable hose and tools</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GL3ZR1JF?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DPGJG95L?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71j+wRZ7ZaL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31NW4G31THL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0GL3ZR1JF</t>
+          <t>B0DPGJG95L</t>
         </is>
       </c>
       <c r="M38" s="14" t="inlineStr">
@@ -15890,13 +15802,13 @@
         </is>
       </c>
       <c r="O38" s="15">
-        <v>16404</v>
+        <v>32719</v>
       </c>
       <c r="P38" s="15">
-        <v>28476</v>
+        <v>247344</v>
       </c>
       <c r="Q38" s="16">
-        <v>0.63</v>
+        <v>0.88</v>
       </c>
       <c r="R38" s="17" t="inlineStr">
         <is>
@@ -15905,61 +15817,55 @@
       </c>
       <c r="S38" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>94</t>
         </is>
       </c>
       <c r="T38" s="15">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="U38" s="16">
-        <v>0.84</v>
+        <v>-0.2</v>
       </c>
       <c r="V38" s="15">
-        <v>11378</v>
-      </c>
-      <c r="W38" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X38" s="15">
-        <v>6325</v>
-      </c>
+        <v>9401</v>
+      </c>
+      <c r="W38" s="15"/>
+      <c r="X38" s="15"/>
       <c r="Y38" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z38" s="20">
-        <v>107.34</v>
+        <v>138.25</v>
       </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="19">
-        <v>36</v>
+        <v>176</v>
       </c>
       <c r="AE38" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF38" s="21">
         <v>4.6</v>
       </c>
       <c r="AG38" s="22">
-        <v>0.028300000000000002</v>
+        <v>0.0147</v>
       </c>
       <c r="AH38" s="20">
-        <v>6.09</v>
+        <v>6.24</v>
       </c>
       <c r="AI38" s="16">
-        <v>0.94</v>
+        <v>0.95</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="13" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2025-02-24</t>
         </is>
       </c>
       <c r="AL38" s="19">
-        <v>231</v>
+        <v>590</v>
       </c>
       <c r="AM38" s="13" t="inlineStr">
         <is>
@@ -15970,10 +15876,10 @@
       <c r="AO38" s="13"/>
       <c r="AP38"/>
       <c r="AQ38" s="19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR38" s="19">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AS38" s="14" t="inlineStr">
         <is>
@@ -16018,42 +15924,38 @@
       </c>
       <c r="BJ38" s="23" t="inlineStr">
         <is>
-          <t>4.67 kg</t>
+          <t>5.9 Kilograms</t>
         </is>
       </c>
       <c r="BK38" s="23" t="inlineStr">
         <is>
-          <t>4.67 kg</t>
+          <t>5.90 kg</t>
         </is>
       </c>
       <c r="BL38" s="23" t="inlineStr">
         <is>
-          <t>26.7 x 41.9 x 34.3 cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="23" t="inlineStr">
-        <is>
-          <t>26.70 x 41.90 x 34.30 cm</t>
-        </is>
-      </c>
+          <t>24D x 36W x 106.7H centimetres</t>
+        </is>
+      </c>
+      <c r="BM38" s="23"/>
       <c r="BN38" s="23" t="inlineStr">
         <is>
-          <t>7.75 kg</t>
+          <t>8.92 kg</t>
         </is>
       </c>
       <c r="BO38" s="23" t="inlineStr">
         <is>
-          <t>7.75 kg</t>
+          <t>8.92 kg</t>
         </is>
       </c>
       <c r="BP38" s="23" t="inlineStr">
         <is>
-          <t>53.5 x 40.5 x 26.7 cm</t>
+          <t>56 x 42 x 27.1 cm</t>
         </is>
       </c>
       <c r="BQ38" s="23" t="inlineStr">
         <is>
-          <t>53.50 x 40.50 x 26.70 cm</t>
+          <t>56.00 x 42.00 x 27.10 cm</t>
         </is>
       </c>
       <c r="BR38" s="13" t="inlineStr">
@@ -16069,45 +15971,45 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="D39" s="14"/>
       <c r="E39" s="14"/>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Swan</t>
         </is>
       </c>
       <c r="G39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Formula Booster for SpotClean 1L 1134NsA cleaning solution booster for use on carpet, upholstery, area</t>
+          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31LC0CHQzZL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="M39" s="14" t="inlineStr">
         <is>
-          <t>Pet Supplies:Dogs:Litter &amp; Housetraining:Odour &amp; Stain Removers</t>
+          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
         </is>
       </c>
       <c r="N39" s="14" t="inlineStr">
@@ -16116,13 +16018,13 @@
         </is>
       </c>
       <c r="O39" s="15">
-        <v>1832</v>
+        <v>33882</v>
       </c>
       <c r="P39" s="15">
-        <v>-397</v>
+        <v>-5408</v>
       </c>
       <c r="Q39" s="16">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
       <c r="R39" s="17" t="inlineStr">
         <is>
@@ -16131,67 +16033,65 @@
       </c>
       <c r="S39" s="18" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T39" s="15">
-        <v>1049</v>
+        <v>216</v>
       </c>
       <c r="U39" s="16">
-        <v>0.11</v>
+        <v>0.83</v>
       </c>
       <c r="V39" s="15">
-        <v>10175</v>
+        <v>8638</v>
       </c>
       <c r="W39" s="15" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X39" s="15">
-        <v>2910</v>
+        <v>4009</v>
       </c>
       <c r="Y39" s="19">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z39" s="20">
-        <v>9.7</v>
+        <v>44.15</v>
       </c>
       <c r="AA39"/>
       <c r="AB39"/>
-      <c r="AC39" s="2">
-        <v>14</v>
-      </c>
+      <c r="AC39" s="2"/>
       <c r="AD39" s="19">
-        <v>9435</v>
+        <v>507</v>
       </c>
       <c r="AE39" s="15">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="AF39" s="21">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AG39" s="22">
-        <v>0.0779</v>
+        <v>0</v>
       </c>
       <c r="AH39" s="20">
-        <v>3.1</v>
+        <v>3.43</v>
       </c>
       <c r="AI39" s="16">
-        <v>0.68</v>
+        <v>0.91</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="13" t="inlineStr">
         <is>
-          <t>2019-12-19</t>
+          <t>2022-06-24</t>
         </is>
       </c>
       <c r="AL39" s="19">
-        <v>2484</v>
+        <v>1567</v>
       </c>
       <c r="AM39" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN39" s="13"/>
@@ -16201,39 +16101,23 @@
         <v>10</v>
       </c>
       <c r="AR39" s="19">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AS39" s="14" t="inlineStr">
         <is>
-          <t>Reliapart</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT39" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU39" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV39" s="14" t="inlineStr">
-        <is>
-          <t>Cardiff Cardiff CF3 2PY GB</t>
-        </is>
-      </c>
-      <c r="AW39" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKGAA3WULFPOP</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU39" s="13"/>
+      <c r="AV39" s="14"/>
+      <c r="AW39" s="13"/>
       <c r="AX39" s="13"/>
-      <c r="AY39" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY39" s="13"/>
       <c r="AZ39" s="13"/>
       <c r="BA39" s="13"/>
       <c r="BB39" s="13"/>
@@ -16251,54 +16135,50 @@
       <c r="BF39" s="13"/>
       <c r="BG39" s="13"/>
       <c r="BH39" s="14"/>
-      <c r="BI39" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI39" s="23"/>
       <c r="BJ39" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BK39" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>2.58 kg</t>
         </is>
       </c>
       <c r="BL39" s="23" t="inlineStr">
         <is>
-          <t>7 x 12 x 23.8 cm</t>
+          <t>23 x 20 x 34 cm</t>
         </is>
       </c>
       <c r="BM39" s="23" t="inlineStr">
         <is>
-          <t>7.00 x 12.00 x 23.80 cm</t>
+          <t>23.00 x 20.00 x 34.00 cm</t>
         </is>
       </c>
       <c r="BN39" s="23" t="inlineStr">
         <is>
-          <t>1.1 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BO39" s="23" t="inlineStr">
         <is>
-          <t>1.10 kg</t>
+          <t>3.29 kg</t>
         </is>
       </c>
       <c r="BP39" s="23" t="inlineStr">
         <is>
-          <t>23.5 x 11.9 x 6.9 cm</t>
+          <t>41.1 x 24.6 x 20.6 cm</t>
         </is>
       </c>
       <c r="BQ39" s="23" t="inlineStr">
         <is>
-          <t>23.50 x 11.90 x 6.90 cm</t>
+          <t>41.10 x 24.60 x 20.60 cm</t>
         </is>
       </c>
       <c r="BR39" s="13" t="inlineStr">
         <is>
-          <t>小包裹</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16309,40 +16189,40 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0DPGJG95L</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>BISSELL</t>
+          <t>Daewoo</t>
         </is>
       </c>
       <c r="G40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0DPGJG95L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>BISSELL PowerWash Compact Pet Upright Carpet &amp; Upholstery Cleaner 4058EsCompact carpet washer with removable hose and tools</t>
+          <t>Daewoo Stairmaster Corded Spotwasher</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DPGJG95L?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/31NW4G31THL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0DPGJG95L</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="M40" s="14" t="inlineStr">
@@ -16356,13 +16236,13 @@
         </is>
       </c>
       <c r="O40" s="15">
-        <v>32719</v>
+        <v>22466</v>
       </c>
       <c r="P40" s="15">
-        <v>247344</v>
+        <v>5586</v>
       </c>
       <c r="Q40" s="16">
-        <v>0.88</v>
+        <v>0.19</v>
       </c>
       <c r="R40" s="17" t="inlineStr">
         <is>
@@ -16371,83 +16251,101 @@
       </c>
       <c r="S40" s="18" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T40" s="15">
-        <v>68</v>
+        <v>177</v>
       </c>
       <c r="U40" s="16">
-        <v>-0.2</v>
+        <v>0.13</v>
       </c>
       <c r="V40" s="15">
-        <v>9401</v>
-      </c>
-      <c r="W40" s="15"/>
-      <c r="X40" s="15"/>
+        <v>8489</v>
+      </c>
+      <c r="W40" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X40" s="15">
+        <v>2398</v>
+      </c>
       <c r="Y40" s="19">
         <v>2</v>
       </c>
       <c r="Z40" s="20">
-        <v>138.25</v>
+        <v>52.75</v>
       </c>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="19">
-        <v>176</v>
+        <v>319</v>
       </c>
       <c r="AE40" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AF40" s="21">
-        <v>4.6</v>
+        <v>3.9</v>
       </c>
       <c r="AG40" s="22">
-        <v>0.0147</v>
+        <v>0.0226</v>
       </c>
       <c r="AH40" s="20">
-        <v>6.24</v>
+        <v>3.61</v>
       </c>
       <c r="AI40" s="16">
-        <v>0.95</v>
+        <v>0.92</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="13" t="inlineStr">
         <is>
-          <t>2025-02-24</t>
+          <t>2024-04-04</t>
         </is>
       </c>
       <c r="AL40" s="19">
-        <v>590</v>
+        <v>916</v>
       </c>
       <c r="AM40" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN40" s="13"/>
       <c r="AO40" s="13"/>
       <c r="AP40"/>
       <c r="AQ40" s="19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AR40" s="19">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS40" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>UK Direct 247</t>
         </is>
       </c>
       <c r="AT40" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU40" s="13"/>
-      <c r="AV40" s="14"/>
-      <c r="AW40" s="13"/>
+          <t>FBM</t>
+        </is>
+      </c>
+      <c r="AU40" s="13" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="AV40" s="14" t="inlineStr">
+        <is>
+          <t>Middx TW14 9LQ GB</t>
+        </is>
+      </c>
+      <c r="AW40" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ</t>
+        </is>
+      </c>
       <c r="AX40" s="13"/>
       <c r="AY40" s="13" t="inlineStr">
         <is>
@@ -16457,11 +16355,7 @@
       <c r="AZ40" s="13"/>
       <c r="BA40" s="13"/>
       <c r="BB40" s="13"/>
-      <c r="BC40" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC40" s="13"/>
       <c r="BD40" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16478,43 +16372,47 @@
       </c>
       <c r="BJ40" s="23" t="inlineStr">
         <is>
-          <t>5.9 Kilograms</t>
+          <t>2.5 kg</t>
         </is>
       </c>
       <c r="BK40" s="23" t="inlineStr">
         <is>
-          <t>5.90 kg</t>
+          <t>2.50 kg</t>
         </is>
       </c>
       <c r="BL40" s="23" t="inlineStr">
         <is>
-          <t>24D x 36W x 106.7H centimetres</t>
-        </is>
-      </c>
-      <c r="BM40" s="23"/>
+          <t>35 x 20 x 23 cm</t>
+        </is>
+      </c>
+      <c r="BM40" s="23" t="inlineStr">
+        <is>
+          <t>35.00 x 20.00 x 23.00 cm</t>
+        </is>
+      </c>
       <c r="BN40" s="23" t="inlineStr">
         <is>
-          <t>8.92 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BO40" s="23" t="inlineStr">
         <is>
-          <t>8.92 kg</t>
+          <t>3.24 kg</t>
         </is>
       </c>
       <c r="BP40" s="23" t="inlineStr">
         <is>
-          <t>56 x 42 x 27.1 cm</t>
+          <t>41.5 x 25.5 x 20.1 cm</t>
         </is>
       </c>
       <c r="BQ40" s="23" t="inlineStr">
         <is>
-          <t>56.00 x 42.00 x 27.10 cm</t>
+          <t>41.50 x 25.50 x 20.10 cm</t>
         </is>
       </c>
       <c r="BR40" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -16525,40 +16423,40 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B0HGKV75WF</t>
         </is>
       </c>
       <c r="D41" s="14"/>
       <c r="E41" s="14"/>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>Swan</t>
+          <t>STARRYBOT</t>
         </is>
       </c>
       <c r="G41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/WelcometoJuibaoHomeLife/page/59D05DFD-B4BC-4B79-9C37-39738D5979A4?lp_asin=B0HGKV75WF&amp;ref_=ast_bln</t>
         </is>
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
+          <t>STARRYBOT Portable Carpet Cleaner, 18KPa, WhitesCompact spot cleaner lifts pet mess, stains and spills from carpets, uphols</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HGKV75WF?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B0HGKV75WF</t>
         </is>
       </c>
       <c r="M41" s="14" t="inlineStr">
@@ -16572,13 +16470,13 @@
         </is>
       </c>
       <c r="O41" s="15">
-        <v>33882</v>
+        <v>41390</v>
       </c>
       <c r="P41" s="15">
-        <v>-5408</v>
+        <v>-37507</v>
       </c>
       <c r="Q41" s="16">
-        <v>-0.19</v>
+        <v>-5.08</v>
       </c>
       <c r="R41" s="17" t="inlineStr">
         <is>
@@ -16587,65 +16485,59 @@
       </c>
       <c r="S41" s="18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>49</t>
         </is>
       </c>
       <c r="T41" s="15">
-        <v>216</v>
+        <v>99</v>
       </c>
       <c r="U41" s="16">
-        <v>0.83</v>
+        <v>88</v>
       </c>
       <c r="V41" s="15">
-        <v>8638</v>
-      </c>
-      <c r="W41" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X41" s="15">
-        <v>4009</v>
-      </c>
+        <v>6534</v>
+      </c>
+      <c r="W41" s="15"/>
+      <c r="X41" s="15"/>
       <c r="Y41" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" s="20">
-        <v>44.15</v>
+        <v>66</v>
       </c>
       <c r="AA41"/>
       <c r="AB41"/>
       <c r="AC41" s="2"/>
       <c r="AD41" s="19">
-        <v>507</v>
+        <v>624</v>
       </c>
       <c r="AE41" s="15">
-        <v>0</v>
+        <v>626</v>
       </c>
       <c r="AF41" s="21">
-        <v>3.8</v>
+        <v>4.7</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
       </c>
       <c r="AH41" s="20">
-        <v>3.43</v>
+        <v>5.33</v>
       </c>
       <c r="AI41" s="16">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AJ41"/>
       <c r="AK41" s="13" t="inlineStr">
         <is>
-          <t>2022-06-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="AL41" s="19">
-        <v>1567</v>
+        <v>40</v>
       </c>
       <c r="AM41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN41" s="13"/>
@@ -16655,21 +16547,33 @@
         <v>10</v>
       </c>
       <c r="AR41" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS41" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>HEYWORK</t>
         </is>
       </c>
       <c r="AT41" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU41" s="13"/>
-      <c r="AV41" s="14"/>
-      <c r="AW41" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU41" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV41" s="14" t="inlineStr">
+        <is>
+          <t>宁波市 浙江 315000 CN</t>
+        </is>
+      </c>
+      <c r="AW41" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ</t>
+        </is>
+      </c>
       <c r="AX41" s="13"/>
       <c r="AY41" s="13"/>
       <c r="AZ41" s="13"/>
@@ -16680,11 +16584,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD41" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD41" s="13"/>
       <c r="BE41" s="13"/>
       <c r="BF41" s="13"/>
       <c r="BG41" s="13"/>
@@ -16692,47 +16592,43 @@
       <c r="BI41" s="23"/>
       <c r="BJ41" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>4.52 kg</t>
         </is>
       </c>
       <c r="BK41" s="23" t="inlineStr">
         <is>
-          <t>2.58 kg</t>
+          <t>4.52 kg</t>
         </is>
       </c>
       <c r="BL41" s="23" t="inlineStr">
         <is>
-          <t>23 x 20 x 34 cm</t>
-        </is>
-      </c>
-      <c r="BM41" s="23" t="inlineStr">
-        <is>
-          <t>23.00 x 20.00 x 34.00 cm</t>
-        </is>
-      </c>
+          <t>35D x 30W x 110H centimetres</t>
+        </is>
+      </c>
+      <c r="BM41" s="23"/>
       <c r="BN41" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>4.6 kg</t>
         </is>
       </c>
       <c r="BO41" s="23" t="inlineStr">
         <is>
-          <t>3.29 kg</t>
+          <t>4.60 kg</t>
         </is>
       </c>
       <c r="BP41" s="23" t="inlineStr">
         <is>
-          <t>41.1 x 24.6 x 20.6 cm</t>
+          <t>46 x 35 x 20 cm</t>
         </is>
       </c>
       <c r="BQ41" s="23" t="inlineStr">
         <is>
-          <t>41.10 x 24.60 x 20.60 cm</t>
+          <t>46.00 x 35.00 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR41" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>轻型标准大件</t>
         </is>
       </c>
     </row>
@@ -16743,40 +16639,40 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B0H4RJFHM6</t>
         </is>
       </c>
       <c r="D42" s="14"/>
       <c r="E42" s="14"/>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>Daewoo</t>
+          <t>dreame</t>
         </is>
       </c>
       <c r="G42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uknull</t>
         </is>
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Daewoo Stairmaster Corded Spotwasher</t>
+          <t>DREAME N20 Steam Portable Carpet Spot Cleaner, 100°C Steams17000 Pa Suction, 70℃ Hot Wash, Fabric &amp; Carpet Cleaning, Versat</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H4RJFHM6?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71sct2oNe0L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B0H4RJFHM6</t>
         </is>
       </c>
       <c r="M42" s="14" t="inlineStr">
@@ -16790,13 +16686,13 @@
         </is>
       </c>
       <c r="O42" s="15">
-        <v>22466</v>
+        <v>37067</v>
       </c>
       <c r="P42" s="15">
-        <v>5586</v>
+        <v>146955</v>
       </c>
       <c r="Q42" s="16">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="R42" s="17" t="inlineStr">
         <is>
@@ -16805,65 +16701,57 @@
       </c>
       <c r="S42" s="18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>45</t>
         </is>
       </c>
       <c r="T42" s="15">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="U42" s="16">
-        <v>0.13</v>
+        <v>12</v>
       </c>
       <c r="V42" s="15">
-        <v>8489</v>
-      </c>
-      <c r="W42" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X42" s="15">
-        <v>2398</v>
-      </c>
+        <v>6218</v>
+      </c>
+      <c r="W42" s="15"/>
+      <c r="X42" s="15"/>
       <c r="Y42" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="20">
-        <v>52.75</v>
+        <v>131.41</v>
       </c>
       <c r="AA42"/>
       <c r="AB42"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="19">
-        <v>319</v>
-      </c>
-      <c r="AE42" s="15">
-        <v>4</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AE42" s="15"/>
       <c r="AF42" s="21">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="AG42" s="22">
-        <v>0.0226</v>
+        <v>0</v>
       </c>
       <c r="AH42" s="20">
-        <v>3.61</v>
+        <v>7.17</v>
       </c>
       <c r="AI42" s="16">
-        <v>0.92</v>
+        <v>0.94</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="13" t="inlineStr">
         <is>
-          <t>2024-04-04</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AL42" s="19">
-        <v>916</v>
+        <v>93</v>
       </c>
       <c r="AM42" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN42" s="13"/>
@@ -16873,43 +16761,31 @@
         <v>8</v>
       </c>
       <c r="AR42" s="19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AS42" s="14" t="inlineStr">
         <is>
-          <t>UK Direct 247</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT42" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
-        </is>
-      </c>
-      <c r="AU42" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV42" s="14" t="inlineStr">
-        <is>
-          <t>Middx TW14 9LQ GB</t>
-        </is>
-      </c>
-      <c r="AW42" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU42" s="13"/>
+      <c r="AV42" s="14"/>
+      <c r="AW42" s="13"/>
       <c r="AX42" s="13"/>
-      <c r="AY42" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="13"/>
       <c r="AZ42" s="13"/>
       <c r="BA42" s="13"/>
       <c r="BB42" s="13"/>
-      <c r="BC42" s="13"/>
+      <c r="BC42" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD42" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -16919,54 +16795,42 @@
       <c r="BF42" s="13"/>
       <c r="BG42" s="13"/>
       <c r="BH42" s="14"/>
-      <c r="BI42" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
+      <c r="BI42" s="23"/>
       <c r="BJ42" s="23" t="inlineStr">
         <is>
-          <t>2.5 kg</t>
+          <t>21 kg</t>
         </is>
       </c>
       <c r="BK42" s="23" t="inlineStr">
         <is>
-          <t>2.50 kg</t>
-        </is>
-      </c>
-      <c r="BL42" s="23" t="inlineStr">
-        <is>
-          <t>35 x 20 x 23 cm</t>
-        </is>
-      </c>
-      <c r="BM42" s="23" t="inlineStr">
-        <is>
-          <t>35.00 x 20.00 x 23.00 cm</t>
-        </is>
-      </c>
+          <t>21.00 kg</t>
+        </is>
+      </c>
+      <c r="BL42" s="23"/>
+      <c r="BM42" s="23"/>
       <c r="BN42" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>21 kg</t>
         </is>
       </c>
       <c r="BO42" s="23" t="inlineStr">
         <is>
-          <t>3.24 kg</t>
+          <t>21.00 kg</t>
         </is>
       </c>
       <c r="BP42" s="23" t="inlineStr">
         <is>
-          <t>41.5 x 25.5 x 20.1 cm</t>
+          <t>61 x 45.5 x 36 cm</t>
         </is>
       </c>
       <c r="BQ42" s="23" t="inlineStr">
         <is>
-          <t>41.50 x 25.50 x 20.10 cm</t>
+          <t>61.00 x 45.50 x 36.00 cm</t>
         </is>
       </c>
       <c r="BR42" s="13" t="inlineStr">
         <is>
-          <t>标准包裹</t>
+          <t>重型标准大件</t>
         </is>
       </c>
     </row>
@@ -16977,40 +16841,40 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0HGKV75WF</t>
+          <t>B081427M5C</t>
         </is>
       </c>
       <c r="D43" s="14"/>
       <c r="E43" s="14"/>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>STARRYBOT</t>
+          <t>Rug Doctor</t>
         </is>
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/WelcometoJuibaoHomeLife/page/59D05DFD-B4BC-4B79-9C37-39738D5979A4?lp_asin=B0HGKV75WF&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B081427M5C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>STARRYBOT Portable Carpet Cleaner, 18KPa, WhitesCompact spot cleaner lifts pet mess, stains and spills from carpets, uphols</t>
+          <t>Rug Doctor Pet Portable Spot Carpet CleanersRubberised Bristles for Pet Hair Removal - 2X Suction - Handheld Carpet &amp; Uphol</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0HGKV75WF?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B081427M5C?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51l75+jHxUL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0HGKV75WF</t>
+          <t>B081427M5C</t>
         </is>
       </c>
       <c r="M43" s="14" t="inlineStr">
@@ -17024,13 +16888,13 @@
         </is>
       </c>
       <c r="O43" s="15">
-        <v>41390</v>
+        <v>88891</v>
       </c>
       <c r="P43" s="15">
-        <v>-37507</v>
+        <v>2455</v>
       </c>
       <c r="Q43" s="16">
-        <v>-5.08</v>
+        <v>0.03</v>
       </c>
       <c r="R43" s="17" t="inlineStr">
         <is>
@@ -17039,59 +16903,67 @@
       </c>
       <c r="S43" s="18" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>52</t>
         </is>
       </c>
       <c r="T43" s="15">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="U43" s="16">
-        <v>88</v>
+        <v>0.64</v>
       </c>
       <c r="V43" s="15">
-        <v>6534</v>
-      </c>
-      <c r="W43" s="15"/>
-      <c r="X43" s="15"/>
+        <v>5620</v>
+      </c>
+      <c r="W43" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X43" s="15">
+        <v>6950</v>
+      </c>
       <c r="Y43" s="19">
         <v>1</v>
       </c>
       <c r="Z43" s="20">
-        <v>66</v>
+        <v>186.61</v>
       </c>
       <c r="AA43"/>
       <c r="AB43"/>
-      <c r="AC43" s="2"/>
+      <c r="AC43" s="2">
+        <v>10</v>
+      </c>
       <c r="AD43" s="19">
-        <v>624</v>
+        <v>238</v>
       </c>
       <c r="AE43" s="15">
-        <v>626</v>
+        <v>0</v>
       </c>
       <c r="AF43" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="22">
         <v>0</v>
       </c>
       <c r="AH43" s="20">
-        <v>5.33</v>
+        <v>6.24</v>
       </c>
       <c r="AI43" s="16">
-        <v>0.92</v>
+        <v>0.95</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="13" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2019-11-27</t>
         </is>
       </c>
       <c r="AL43" s="19">
-        <v>40</v>
+        <v>2507</v>
       </c>
       <c r="AM43" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>AMZ</t>
         </is>
       </c>
       <c r="AN43" s="13"/>
@@ -17105,29 +16977,17 @@
       </c>
       <c r="AS43" s="14" t="inlineStr">
         <is>
-          <t>HEYWORK</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT43" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU43" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV43" s="14" t="inlineStr">
-        <is>
-          <t>宁波市 浙江 315000 CN</t>
-        </is>
-      </c>
-      <c r="AW43" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU43" s="13"/>
+      <c r="AV43" s="14"/>
+      <c r="AW43" s="13"/>
       <c r="AX43" s="13"/>
       <c r="AY43" s="13"/>
       <c r="AZ43" s="13"/>
@@ -17138,7 +16998,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD43" s="13"/>
+      <c r="BD43" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE43" s="13"/>
       <c r="BF43" s="13"/>
       <c r="BG43" s="13"/>
@@ -17146,38 +17010,42 @@
       <c r="BI43" s="23"/>
       <c r="BJ43" s="23" t="inlineStr">
         <is>
-          <t>4.52 kg</t>
+          <t>7.45 kg</t>
         </is>
       </c>
       <c r="BK43" s="23" t="inlineStr">
         <is>
-          <t>4.52 kg</t>
+          <t>7.45 kg</t>
         </is>
       </c>
       <c r="BL43" s="23" t="inlineStr">
         <is>
-          <t>35D x 30W x 110H centimetres</t>
-        </is>
-      </c>
-      <c r="BM43" s="23"/>
+          <t>31.75 x 45 x 43.8 cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="23" t="inlineStr">
+        <is>
+          <t>31.75 x 45.00 x 43.80 cm</t>
+        </is>
+      </c>
       <c r="BN43" s="23" t="inlineStr">
         <is>
-          <t>4.6 kg</t>
+          <t>8.92 kg</t>
         </is>
       </c>
       <c r="BO43" s="23" t="inlineStr">
         <is>
-          <t>4.60 kg</t>
+          <t>8.92 kg</t>
         </is>
       </c>
       <c r="BP43" s="23" t="inlineStr">
         <is>
-          <t>46 x 35 x 20 cm</t>
+          <t>45.5 x 44 x 32 cm</t>
         </is>
       </c>
       <c r="BQ43" s="23" t="inlineStr">
         <is>
-          <t>46.00 x 35.00 x 20.00 cm</t>
+          <t>45.50 x 44.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BR43" s="13" t="inlineStr">
@@ -17193,40 +17061,40 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0H4RJFHM6</t>
+          <t>B0HC3856PH</t>
         </is>
       </c>
       <c r="D44" s="14"/>
       <c r="E44" s="14"/>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>dreame</t>
+          <t>Gloppers</t>
         </is>
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uknull</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gloppers</t>
         </is>
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>DREAME N20 Steam Portable Carpet Spot Cleaner, 100°C Steams17000 Pa Suction, 70℃ Hot Wash, Fabric &amp; Carpet Cleaning, Versat</t>
+          <t>Gloppers Carpet and Upholstery Cleaner, 12kpa Portable Rug Cleaner Machine, 450W Handheld Wet Vacuum Machine with Separate Ta</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H4RJFHM6?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HC3856PH?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71sct2oNe0L._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61O26S3eC8L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0H4RJFHM6</t>
+          <t>B0HC3856PH</t>
         </is>
       </c>
       <c r="M44" s="14" t="inlineStr">
@@ -17240,13 +17108,13 @@
         </is>
       </c>
       <c r="O44" s="15">
-        <v>37067</v>
+        <v>18241</v>
       </c>
       <c r="P44" s="15">
-        <v>146955</v>
+        <v>23954</v>
       </c>
       <c r="Q44" s="16">
-        <v>0.8</v>
+        <v>0.57</v>
       </c>
       <c r="R44" s="17" t="inlineStr">
         <is>
@@ -17255,17 +17123,15 @@
       </c>
       <c r="S44" s="18" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>31</t>
         </is>
       </c>
       <c r="T44" s="15">
-        <v>55</v>
-      </c>
-      <c r="U44" s="16">
-        <v>12</v>
-      </c>
+        <v>81</v>
+      </c>
+      <c r="U44" s="16"/>
       <c r="V44" s="15">
-        <v>6218</v>
+        <v>5102</v>
       </c>
       <c r="W44" s="15"/>
       <c r="X44" s="15"/>
@@ -17273,23 +17139,25 @@
         <v>1</v>
       </c>
       <c r="Z44" s="20">
-        <v>131.41</v>
+        <v>62.99</v>
       </c>
       <c r="AA44"/>
       <c r="AB44"/>
       <c r="AC44" s="2"/>
       <c r="AD44" s="19">
-        <v>1</v>
-      </c>
-      <c r="AE44" s="15"/>
+        <v>5</v>
+      </c>
+      <c r="AE44" s="15">
+        <v>2</v>
+      </c>
       <c r="AF44" s="21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AG44" s="22">
-        <v>0</v>
+        <v>0.024700000000000003</v>
       </c>
       <c r="AH44" s="20">
-        <v>7.17</v>
+        <v>3.62</v>
       </c>
       <c r="AI44" s="16">
         <v>0.94</v>
@@ -17297,15 +17165,15 @@
       <c r="AJ44"/>
       <c r="AK44" s="13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AL44" s="19">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="AM44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN44" s="13"/>
@@ -17319,17 +17187,29 @@
       </c>
       <c r="AS44" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>PUXI Tech</t>
         </is>
       </c>
       <c r="AT44" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU44" s="13"/>
-      <c r="AV44" s="14"/>
-      <c r="AW44" s="13"/>
+          <t>FBA</t>
+        </is>
+      </c>
+      <c r="AU44" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV44" s="14" t="inlineStr">
+        <is>
+          <t>上海市 上海 201316 CN</t>
+        </is>
+      </c>
+      <c r="AW44" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9YABL1QACO9J</t>
+        </is>
+      </c>
       <c r="AX44" s="13"/>
       <c r="AY44" s="13"/>
       <c r="AZ44" s="13"/>
@@ -17352,39 +17232,47 @@
       <c r="BI44" s="23"/>
       <c r="BJ44" s="23" t="inlineStr">
         <is>
-          <t>21 kg</t>
+          <t>4 kg</t>
         </is>
       </c>
       <c r="BK44" s="23" t="inlineStr">
         <is>
-          <t>21.00 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="23"/>
-      <c r="BM44" s="23"/>
+          <t>4.00 kg</t>
+        </is>
+      </c>
+      <c r="BL44" s="23" t="inlineStr">
+        <is>
+          <t>15 x 30 x 32 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="23" t="inlineStr">
+        <is>
+          <t>15.00 x 30.00 x 32.00 cm</t>
+        </is>
+      </c>
       <c r="BN44" s="23" t="inlineStr">
         <is>
-          <t>21 kg</t>
+          <t>4.5 kg</t>
         </is>
       </c>
       <c r="BO44" s="23" t="inlineStr">
         <is>
-          <t>21.00 kg</t>
+          <t>4.50 kg</t>
         </is>
       </c>
       <c r="BP44" s="23" t="inlineStr">
         <is>
-          <t>61 x 45.5 x 36 cm</t>
+          <t>41 x 32 x 24 cm</t>
         </is>
       </c>
       <c r="BQ44" s="23" t="inlineStr">
         <is>
-          <t>61.00 x 45.50 x 36.00 cm</t>
+          <t>41.00 x 32.00 x 24.00 cm</t>
         </is>
       </c>
       <c r="BR44" s="13" t="inlineStr">
         <is>
-          <t>重型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17395,40 +17283,40 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B081427M5C</t>
+          <t>B09JSVWX57</t>
         </is>
       </c>
       <c r="D45" s="14"/>
       <c r="E45" s="14"/>
       <c r="F45" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor</t>
+          <t>Tower</t>
         </is>
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B081427M5C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor Pet Portable Spot Carpet CleanersRubberised Bristles for Pet Hair Removal - 2X Suction - Handheld Carpet &amp; Uphol</t>
+          <t>Tower T548005 AquajetPlus Spot Cleaner with Suction Nozzle &amp; Brush, 1.2L Clean &amp; Dirty Water Tanks, 1.2m Hose, 400W, Grey &amp; B</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B081427M5C?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09JSVWX57?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51l75+jHxUL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B081427M5C</t>
+          <t>B09JSVWX57</t>
         </is>
       </c>
       <c r="M45" s="14" t="inlineStr">
@@ -17438,36 +17326,38 @@
       </c>
       <c r="N45" s="14" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="O45" s="15">
-        <v>88891</v>
+        <v>17125</v>
       </c>
       <c r="P45" s="15">
-        <v>2455</v>
+        <v>-261</v>
       </c>
       <c r="Q45" s="16">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="R45" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers</t>
+          <t>Carpet Washers
+Home Care &amp; Cleaning</t>
         </is>
       </c>
       <c r="S45" s="18" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>43
+5407</t>
         </is>
       </c>
       <c r="T45" s="15">
-        <v>61</v>
+        <v>102</v>
       </c>
       <c r="U45" s="16">
-        <v>0.64</v>
+        <v>-0.01</v>
       </c>
       <c r="V45" s="15">
-        <v>5620</v>
+        <v>5099</v>
       </c>
       <c r="W45" s="15" t="inlineStr">
         <is>
@@ -17475,45 +17365,43 @@
         </is>
       </c>
       <c r="X45" s="15">
-        <v>6950</v>
+        <v>3157</v>
       </c>
       <c r="Y45" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z45" s="20">
-        <v>186.61</v>
+        <v>66.24</v>
       </c>
       <c r="AA45"/>
       <c r="AB45"/>
-      <c r="AC45" s="2">
-        <v>10</v>
-      </c>
+      <c r="AC45" s="2"/>
       <c r="AD45" s="19">
-        <v>238</v>
+        <v>476</v>
       </c>
       <c r="AE45" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AF45" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG45" s="22">
-        <v>0</v>
+        <v>0.0294</v>
       </c>
       <c r="AH45" s="20">
-        <v>6.24</v>
+        <v>3.43</v>
       </c>
       <c r="AI45" s="16">
-        <v>0.95</v>
+        <v>0.94</v>
       </c>
       <c r="AJ45"/>
       <c r="AK45" s="13" t="inlineStr">
         <is>
-          <t>2019-11-27</t>
+          <t>2021-10-20</t>
         </is>
       </c>
       <c r="AL45" s="19">
-        <v>2507</v>
+        <v>1813</v>
       </c>
       <c r="AM45" s="13" t="inlineStr">
         <is>
@@ -17543,7 +17431,11 @@
       <c r="AV45" s="14"/>
       <c r="AW45" s="13"/>
       <c r="AX45" s="13"/>
-      <c r="AY45" s="13"/>
+      <c r="AY45" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ45" s="13"/>
       <c r="BA45" s="13"/>
       <c r="BB45" s="13"/>
@@ -17561,50 +17453,50 @@
       <c r="BF45" s="13"/>
       <c r="BG45" s="13"/>
       <c r="BH45" s="14"/>
-      <c r="BI45" s="23"/>
+      <c r="BI45" s="23" t="inlineStr">
+        <is>
+          <t>Amazon's Choice</t>
+        </is>
+      </c>
       <c r="BJ45" s="23" t="inlineStr">
         <is>
-          <t>7.45 kg</t>
+          <t>3.5 Kilograms</t>
         </is>
       </c>
       <c r="BK45" s="23" t="inlineStr">
         <is>
-          <t>7.45 kg</t>
+          <t>3.50 kg</t>
         </is>
       </c>
       <c r="BL45" s="23" t="inlineStr">
         <is>
-          <t>31.75 x 45 x 43.8 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="23" t="inlineStr">
-        <is>
-          <t>31.75 x 45.00 x 43.80 cm</t>
-        </is>
-      </c>
+          <t>19L x 27W x 29H centimetres</t>
+        </is>
+      </c>
+      <c r="BM45" s="23"/>
       <c r="BN45" s="23" t="inlineStr">
         <is>
-          <t>8.92 kg</t>
+          <t>3.99 kg</t>
         </is>
       </c>
       <c r="BO45" s="23" t="inlineStr">
         <is>
-          <t>8.92 kg</t>
+          <t>3.99 kg</t>
         </is>
       </c>
       <c r="BP45" s="23" t="inlineStr">
         <is>
-          <t>45.5 x 44 x 32 cm</t>
+          <t>35.7 x 32.6 x 20 cm</t>
         </is>
       </c>
       <c r="BQ45" s="23" t="inlineStr">
         <is>
-          <t>45.50 x 44.00 x 32.00 cm</t>
+          <t>35.70 x 32.60 x 20.00 cm</t>
         </is>
       </c>
       <c r="BR45" s="13" t="inlineStr">
         <is>
-          <t>轻型标准大件</t>
+          <t>标准包裹</t>
         </is>
       </c>
     </row>
@@ -17615,40 +17507,40 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0HC3856PH</t>
+          <t>B0FM3VJXKQ</t>
         </is>
       </c>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14" t="inlineStr">
         <is>
-          <t>Gloppers</t>
+          <t>Vlihapy</t>
         </is>
       </c>
       <c r="G46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gloppers</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
         </is>
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Gloppers Carpet and Upholstery Cleaner, 12kpa Portable Rug Cleaner Machine, 450W Handheld Wet Vacuum Machine with Separate Ta</t>
+          <t>Home Pet-Design Spot Cleaner, Fabric, Stain, Car Seats, Upholstery, Pet Messes, Sofa and Carpet Cleaning Machine, 450W Portab</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0HC3856PH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FM3VJXKQ?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61O26S3eC8L._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41nOwlawyOL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0HC3856PH</t>
+          <t>B0FM3VJXKQ</t>
         </is>
       </c>
       <c r="M46" s="14" t="inlineStr">
@@ -17662,13 +17554,13 @@
         </is>
       </c>
       <c r="O46" s="15">
-        <v>18241</v>
+        <v>39203</v>
       </c>
       <c r="P46" s="15">
-        <v>23954</v>
+        <v>21357</v>
       </c>
       <c r="Q46" s="16">
-        <v>0.57</v>
+        <v>0.35</v>
       </c>
       <c r="R46" s="17" t="inlineStr">
         <is>
@@ -17677,76 +17569,82 @@
       </c>
       <c r="S46" s="18" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T46" s="15">
-        <v>81</v>
-      </c>
-      <c r="U46" s="16"/>
+        <v>117</v>
+      </c>
+      <c r="U46" s="16">
+        <v>0.61</v>
+      </c>
       <c r="V46" s="15">
-        <v>5102</v>
-      </c>
-      <c r="W46" s="15"/>
-      <c r="X46" s="15"/>
+        <v>4046</v>
+      </c>
+      <c r="W46" s="15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X46" s="15">
+        <v>2279</v>
+      </c>
       <c r="Y46" s="19">
         <v>1</v>
       </c>
       <c r="Z46" s="20">
-        <v>62.99</v>
+        <v>34.58</v>
       </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46" s="2"/>
       <c r="AD46" s="19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE46" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF46" s="21">
         <v>5</v>
       </c>
       <c r="AG46" s="22">
-        <v>0.024700000000000003</v>
-      </c>
-      <c r="AH46" s="20">
-        <v>3.62</v>
-      </c>
+        <v>0.0085</v>
+      </c>
+      <c r="AH46" s="20"/>
       <c r="AI46" s="16">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="AJ46"/>
       <c r="AK46" s="13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AL46" s="19">
-        <v>12</v>
+        <v>419</v>
       </c>
       <c r="AM46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AN46" s="13"/>
       <c r="AO46" s="13"/>
       <c r="AP46"/>
       <c r="AQ46" s="19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR46" s="19">
         <v>1</v>
       </c>
       <c r="AS46" s="14" t="inlineStr">
         <is>
-          <t>PUXI Tech</t>
+          <t>Treasuretool</t>
         </is>
       </c>
       <c r="AT46" s="13" t="inlineStr">
         <is>
-          <t>FBA</t>
+          <t>FBM</t>
         </is>
       </c>
       <c r="AU46" s="13" t="inlineStr">
@@ -17756,12 +17654,12 @@
       </c>
       <c r="AV46" s="14" t="inlineStr">
         <is>
-          <t>上海市 上海 201316 CN</t>
+          <t>南通市 崇川区 江苏省 226014 CN</t>
         </is>
       </c>
       <c r="AW46" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9YABL1QACO9J</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
         </is>
       </c>
       <c r="AX46" s="13"/>
@@ -17769,11 +17667,7 @@
       <c r="AZ46" s="13"/>
       <c r="BA46" s="13"/>
       <c r="BB46" s="13"/>
-      <c r="BC46" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC46" s="13"/>
       <c r="BD46" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -17784,51 +17678,19 @@
       <c r="BG46" s="13"/>
       <c r="BH46" s="14"/>
       <c r="BI46" s="23"/>
-      <c r="BJ46" s="23" t="inlineStr">
-        <is>
-          <t>4 kg</t>
-        </is>
-      </c>
-      <c r="BK46" s="23" t="inlineStr">
-        <is>
-          <t>4.00 kg</t>
-        </is>
-      </c>
+      <c r="BJ46" s="23"/>
+      <c r="BK46" s="23"/>
       <c r="BL46" s="23" t="inlineStr">
         <is>
-          <t>15 x 30 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BM46" s="23" t="inlineStr">
-        <is>
-          <t>15.00 x 30.00 x 32.00 cm</t>
-        </is>
-      </c>
-      <c r="BN46" s="23" t="inlineStr">
-        <is>
-          <t>4.5 kg</t>
-        </is>
-      </c>
-      <c r="BO46" s="23" t="inlineStr">
-        <is>
-          <t>4.50 kg</t>
-        </is>
-      </c>
-      <c r="BP46" s="23" t="inlineStr">
-        <is>
-          <t>41 x 32 x 24 cm</t>
-        </is>
-      </c>
-      <c r="BQ46" s="23" t="inlineStr">
-        <is>
-          <t>41.00 x 32.00 x 24.00 cm</t>
-        </is>
-      </c>
-      <c r="BR46" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+          <t>29D x 16W x 32.5H centimetres</t>
+        </is>
+      </c>
+      <c r="BM46" s="23"/>
+      <c r="BN46" s="23"/>
+      <c r="BO46" s="23"/>
+      <c r="BP46" s="23"/>
+      <c r="BQ46" s="23"/>
+      <c r="BR46" s="13"/>
     </row>
     <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
@@ -17837,40 +17699,40 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B09JSVWX57</t>
+          <t>B0FKGYK25M</t>
         </is>
       </c>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="14" t="inlineStr">
         <is>
-          <t>Tower</t>
+          <t>VickyHome</t>
         </is>
       </c>
       <c r="G47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome</t>
         </is>
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Tower T548005 AquajetPlus Spot Cleaner with Suction Nozzle &amp; Brush, 1.2L Clean &amp; Dirty Water Tanks, 1.2m Hose, 400W, Grey &amp; B</t>
+          <t>VickyHome Spot Cleaner, 450W Portable Carpet &amp; Upholstery Cleaner Sofa and Carpet Cleaning Machine, Lightweight Handheld Floo</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09JSVWX57?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B09JSVWX57</t>
+          <t>B0FKGYK25M</t>
         </is>
       </c>
       <c r="M47" s="14" t="inlineStr">
@@ -17880,38 +17742,36 @@
       </c>
       <c r="N47" s="14" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="O47" s="15">
-        <v>17125</v>
+        <v>48523</v>
       </c>
       <c r="P47" s="15">
-        <v>-261</v>
+        <v>1602</v>
       </c>
       <c r="Q47" s="16">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R47" s="17" t="inlineStr">
         <is>
-          <t>Carpet Washers
-Home Care &amp; Cleaning</t>
+          <t>Carpet Washers</t>
         </is>
       </c>
       <c r="S47" s="18" t="inlineStr">
         <is>
-          <t>43
-5407</t>
+          <t>51</t>
         </is>
       </c>
       <c r="T47" s="15">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="U47" s="16">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="V47" s="15">
-        <v>5099</v>
+        <v>3664</v>
       </c>
       <c r="W47" s="15" t="inlineStr">
         <is>
@@ -17919,140 +17779,102 @@
         </is>
       </c>
       <c r="X47" s="15">
-        <v>3157</v>
+        <v>2248</v>
       </c>
       <c r="Y47" s="19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z47" s="20">
-        <v>66.24</v>
+        <v>35.57</v>
       </c>
       <c r="AA47"/>
       <c r="AB47"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="19">
-        <v>476</v>
+        <v>29</v>
       </c>
       <c r="AE47" s="15">
         <v>3</v>
       </c>
       <c r="AF47" s="21">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AG47" s="22">
-        <v>0.0294</v>
-      </c>
-      <c r="AH47" s="20">
-        <v>3.43</v>
-      </c>
+        <v>0.0291</v>
+      </c>
+      <c r="AH47" s="20"/>
       <c r="AI47" s="16">
-        <v>0.94</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
       <c r="AK47" s="13" t="inlineStr">
         <is>
-          <t>2021-10-20</t>
+          <t>2025-08-02</t>
         </is>
       </c>
       <c r="AL47" s="19">
-        <v>1813</v>
+        <v>432</v>
       </c>
       <c r="AM47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AN47" s="13"/>
       <c r="AO47" s="13"/>
       <c r="AP47"/>
       <c r="AQ47" s="19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR47" s="19">
         <v>1</v>
       </c>
       <c r="AS47" s="14" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>Lucn</t>
         </is>
       </c>
       <c r="AT47" s="13" t="inlineStr">
         <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU47" s="13"/>
-      <c r="AV47" s="14"/>
-      <c r="AW47" s="13"/>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU47" s="13" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV47" s="14" t="inlineStr">
+        <is>
+          <t>Zengchengqu Guangdongsheng 511300 CN</t>
+        </is>
+      </c>
+      <c r="AW47" s="13" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U</t>
+        </is>
+      </c>
       <c r="AX47" s="13"/>
-      <c r="AY47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY47" s="13"/>
       <c r="AZ47" s="13"/>
       <c r="BA47" s="13"/>
       <c r="BB47" s="13"/>
-      <c r="BC47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD47" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC47" s="13"/>
+      <c r="BD47" s="13"/>
       <c r="BE47" s="13"/>
       <c r="BF47" s="13"/>
       <c r="BG47" s="13"/>
       <c r="BH47" s="14"/>
-      <c r="BI47" s="23" t="inlineStr">
-        <is>
-          <t>Amazon's Choice</t>
-        </is>
-      </c>
-      <c r="BJ47" s="23" t="inlineStr">
-        <is>
-          <t>3.5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK47" s="23" t="inlineStr">
-        <is>
-          <t>3.50 kg</t>
-        </is>
-      </c>
-      <c r="BL47" s="23" t="inlineStr">
-        <is>
-          <t>19L x 27W x 29H centimetres</t>
-        </is>
-      </c>
+      <c r="BI47" s="23"/>
+      <c r="BJ47" s="23"/>
+      <c r="BK47" s="23"/>
+      <c r="BL47" s="23"/>
       <c r="BM47" s="23"/>
-      <c r="BN47" s="23" t="inlineStr">
-        <is>
-          <t>3.99 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="23" t="inlineStr">
-        <is>
-          <t>3.99 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="23" t="inlineStr">
-        <is>
-          <t>35.7 x 32.6 x 20 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="23" t="inlineStr">
-        <is>
-          <t>35.70 x 32.60 x 20.00 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="13" t="inlineStr">
-        <is>
-          <t>标准包裹</t>
-        </is>
-      </c>
+      <c r="BN47" s="23"/>
+      <c r="BO47" s="23"/>
+      <c r="BP47" s="23"/>
+      <c r="BQ47" s="23"/>
+      <c r="BR47" s="13"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -18061,40 +17883,40 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0FM3VJXKQ</t>
+          <t>B0H8NPR9ZW</t>
         </is>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>Vlihapy</t>
+          <t>PUREBEAR</t>
         </is>
       </c>
       <c r="G48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy</t>
+          <t>https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8NPR9ZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Home Pet-Design Spot Cleaner, Fabric, Stain, Car Seats, Upholstery, Pet Messes, Sofa and Carpet Cleaning Machine, 450W Portab</t>
+          <t>PUREBEAR Multi-Purpose Portable Upholstery &amp; Carpets18Kpa Suction Power| Dual Tank| Upholstery| Powerful Suction Spot Clean</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FM3VJXKQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H8NPR9ZW?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41nOwlawyOL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71wZpLFoJpL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0FM3VJXKQ</t>
+          <t>B0H8NPR9ZW</t>
         </is>
       </c>
       <c r="M48" s="14" t="inlineStr">
@@ -18108,13 +17930,13 @@
         </is>
       </c>
       <c r="O48" s="15">
-        <v>39203</v>
+        <v>28098</v>
       </c>
       <c r="P48" s="15">
-        <v>21357</v>
+        <v>22851</v>
       </c>
       <c r="Q48" s="16">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="R48" s="17" t="inlineStr">
         <is>
@@ -18123,82 +17945,76 @@
       </c>
       <c r="S48" s="18" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T48" s="15">
-        <v>117</v>
-      </c>
-      <c r="U48" s="16">
-        <v>0.61</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="U48" s="16"/>
       <c r="V48" s="15">
-        <v>4046</v>
-      </c>
-      <c r="W48" s="15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X48" s="15">
-        <v>2279</v>
-      </c>
+        <v>2640</v>
+      </c>
+      <c r="W48" s="15"/>
+      <c r="X48" s="15"/>
       <c r="Y48" s="19">
         <v>1</v>
       </c>
       <c r="Z48" s="20">
-        <v>34.58</v>
+        <v>59.99</v>
       </c>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48" s="2"/>
       <c r="AD48" s="19">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AE48" s="15">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="AF48" s="21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AG48" s="22">
-        <v>0.0085</v>
-      </c>
-      <c r="AH48" s="20"/>
+        <v>0.4318</v>
+      </c>
+      <c r="AH48" s="20">
+        <v>5.33</v>
+      </c>
       <c r="AI48" s="16">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="AJ48"/>
       <c r="AK48" s="13" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AL48" s="19">
-        <v>419</v>
+        <v>28</v>
       </c>
       <c r="AM48" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN48" s="13"/>
       <c r="AO48" s="13"/>
       <c r="AP48"/>
       <c r="AQ48" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR48" s="19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS48" s="14" t="inlineStr">
         <is>
-          <t>Treasuretool</t>
+          <t>Xinhua County Hongxu Trading Co., Ltd</t>
         </is>
       </c>
       <c r="AT48" s="13" t="inlineStr">
         <is>
-          <t>FBM</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU48" s="13" t="inlineStr">
@@ -18208,12 +18024,12 @@
       </c>
       <c r="AV48" s="14" t="inlineStr">
         <is>
-          <t>南通市 崇川区 江苏省 226014 CN</t>
+          <t>hunansheng 417600 CN</t>
         </is>
       </c>
       <c r="AW48" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL</t>
         </is>
       </c>
       <c r="AX48" s="13"/>
@@ -18221,7 +18037,11 @@
       <c r="AZ48" s="13"/>
       <c r="BA48" s="13"/>
       <c r="BB48" s="13"/>
-      <c r="BC48" s="13"/>
+      <c r="BC48" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD48" s="13" t="inlineStr">
         <is>
           <t>Y</t>
@@ -18232,19 +18052,43 @@
       <c r="BG48" s="13"/>
       <c r="BH48" s="14"/>
       <c r="BI48" s="23"/>
-      <c r="BJ48" s="23"/>
-      <c r="BK48" s="23"/>
-      <c r="BL48" s="23" t="inlineStr">
-        <is>
-          <t>29D x 16W x 32.5H centimetres</t>
-        </is>
-      </c>
+      <c r="BJ48" s="23" t="inlineStr">
+        <is>
+          <t>4.14 kg</t>
+        </is>
+      </c>
+      <c r="BK48" s="23" t="inlineStr">
+        <is>
+          <t>4.14 kg</t>
+        </is>
+      </c>
+      <c r="BL48" s="23"/>
       <c r="BM48" s="23"/>
-      <c r="BN48" s="23"/>
-      <c r="BO48" s="23"/>
-      <c r="BP48" s="23"/>
-      <c r="BQ48" s="23"/>
-      <c r="BR48" s="13"/>
+      <c r="BN48" s="23" t="inlineStr">
+        <is>
+          <t>4.14 kg</t>
+        </is>
+      </c>
+      <c r="BO48" s="23" t="inlineStr">
+        <is>
+          <t>4.14 kg</t>
+        </is>
+      </c>
+      <c r="BP48" s="23" t="inlineStr">
+        <is>
+          <t>42.5 x 35.7 x 20.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ48" s="23" t="inlineStr">
+        <is>
+          <t>42.50 x 35.70 x 20.20 cm</t>
+        </is>
+      </c>
+      <c r="BR48" s="13" t="inlineStr">
+        <is>
+          <t>轻型标准大件</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -18253,40 +18097,40 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0FKGYK25M</t>
+          <t>B01LX6WOFS</t>
         </is>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>VickyHome</t>
+          <t>Ecozone</t>
         </is>
       </c>
       <c r="G49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome</t>
+          <t>https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>VickyHome Spot Cleaner, 450W Portable Carpet &amp; Upholstery Cleaner Sofa and Carpet Cleaning Machine, Lightweight Handheld Floo</t>
+          <t>EcoZone Carpet Shampoo Solution, Deep Cleans Upholstery, Manual &amp; Machine Cleaning, Fresh Cotton Scent, 3-in-1 Plant Based St</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0FKGYK25M</t>
+          <t>B01LX6WOFS</t>
         </is>
       </c>
       <c r="M49" s="14" t="inlineStr">
@@ -18300,13 +18144,13 @@
         </is>
       </c>
       <c r="O49" s="15">
-        <v>48523</v>
+        <v>35994</v>
       </c>
       <c r="P49" s="15">
-        <v>1602</v>
+        <v>-5051</v>
       </c>
       <c r="Q49" s="16">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="R49" s="17" t="inlineStr">
         <is>
@@ -18315,570 +18159,172 @@
       </c>
       <c r="S49" s="18" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>44</t>
         </is>
       </c>
       <c r="T49" s="15">
-        <v>103</v>
+        <v>186</v>
       </c>
       <c r="U49" s="16">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="V49" s="15">
-        <v>3664</v>
+        <v>1585</v>
       </c>
       <c r="W49" s="15" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="X49" s="15">
-        <v>2248</v>
+        <v>831</v>
       </c>
       <c r="Y49" s="19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="20">
-        <v>35.57</v>
+        <v>8.52</v>
       </c>
       <c r="AA49"/>
       <c r="AB49"/>
-      <c r="AC49" s="2"/>
+      <c r="AC49" s="2">
+        <v>9</v>
+      </c>
       <c r="AD49" s="19">
-        <v>29</v>
+        <v>906</v>
       </c>
       <c r="AE49" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF49" s="21">
         <v>4.4</v>
       </c>
       <c r="AG49" s="22">
-        <v>0.0291</v>
-      </c>
-      <c r="AH49" s="20"/>
+        <v>0.0108</v>
+      </c>
+      <c r="AH49" s="20">
+        <v>3.1</v>
+      </c>
       <c r="AI49" s="16">
-        <v>0</v>
+        <v>0.64</v>
       </c>
       <c r="AJ49"/>
       <c r="AK49" s="13" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2017-05-30</t>
         </is>
       </c>
       <c r="AL49" s="19">
-        <v>432</v>
+        <v>3417</v>
       </c>
       <c r="AM49" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AN49" s="13"/>
       <c r="AO49" s="13"/>
       <c r="AP49"/>
       <c r="AQ49" s="19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AR49" s="19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AS49" s="14" t="inlineStr">
         <is>
-          <t>Lucn</t>
+          <t>Siwa Salt Direct</t>
         </is>
       </c>
       <c r="AT49" s="13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>FBA</t>
         </is>
       </c>
       <c r="AU49" s="13" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="AV49" s="14" t="inlineStr">
         <is>
-          <t>Zengchengqu Guangdongsheng 511300 CN</t>
+          <t>Enfield Middlesex EN2 7LL GB</t>
         </is>
       </c>
       <c r="AW49" s="13" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U</t>
+          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1DDI4YT9F1YO7</t>
         </is>
       </c>
       <c r="AX49" s="13"/>
-      <c r="AY49" s="13"/>
+      <c r="AY49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ49" s="13"/>
       <c r="BA49" s="13"/>
       <c r="BB49" s="13"/>
-      <c r="BC49" s="13"/>
-      <c r="BD49" s="13"/>
+      <c r="BC49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD49" s="13" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE49" s="13"/>
       <c r="BF49" s="13"/>
       <c r="BG49" s="13"/>
       <c r="BH49" s="14"/>
-      <c r="BI49" s="23"/>
-      <c r="BJ49" s="23"/>
-      <c r="BK49" s="23"/>
-      <c r="BL49" s="23"/>
-      <c r="BM49" s="23"/>
-      <c r="BN49" s="23"/>
-      <c r="BO49" s="23"/>
-      <c r="BP49" s="23"/>
-      <c r="BQ49" s="23"/>
-      <c r="BR49" s="13"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0H8NPR9ZW</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR</t>
-        </is>
-      </c>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8NPR9ZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>PUREBEAR Multi-Purpose Portable Upholstery &amp; Carpets18Kpa Suction Power| Dual Tank| Upholstery| Powerful Suction Spot Clean</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0H8NPR9ZW?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71wZpLFoJpL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0H8NPR9ZW</t>
-        </is>
-      </c>
-      <c r="M50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O50" s="15">
-        <v>28098</v>
-      </c>
-      <c r="P50" s="15">
-        <v>22851</v>
-      </c>
-      <c r="Q50" s="16">
-        <v>0.45</v>
-      </c>
-      <c r="R50" s="17" t="inlineStr">
-        <is>
-          <t>Carpet Washers</t>
-        </is>
-      </c>
-      <c r="S50" s="18" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="T50" s="15">
-        <v>44</v>
-      </c>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15">
-        <v>2640</v>
-      </c>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="20">
-        <v>59.99</v>
-      </c>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="19">
-        <v>24</v>
-      </c>
-      <c r="AE50" s="15">
-        <v>19</v>
-      </c>
-      <c r="AF50" s="21">
-        <v>4.7</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0.4318</v>
-      </c>
-      <c r="AH50" s="20">
-        <v>5.33</v>
-      </c>
-      <c r="AI50" s="16">
-        <v>0.91</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
-      <c r="AL50" s="19">
-        <v>28</v>
-      </c>
-      <c r="AM50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR50" s="19">
-        <v>2</v>
-      </c>
-      <c r="AS50" s="14" t="inlineStr">
-        <is>
-          <t>Xinhua County Hongxu Trading Co., Ltd</t>
-        </is>
-      </c>
-      <c r="AT50" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU50" s="13" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV50" s="14" t="inlineStr">
-        <is>
-          <t>hunansheng 417600 CN</t>
-        </is>
-      </c>
-      <c r="AW50" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL</t>
-        </is>
-      </c>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD50" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50" s="23"/>
-      <c r="BJ50" s="23" t="inlineStr">
-        <is>
-          <t>4.14 kg</t>
-        </is>
-      </c>
-      <c r="BK50" s="23" t="inlineStr">
-        <is>
-          <t>4.14 kg</t>
-        </is>
-      </c>
-      <c r="BL50" s="23"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50" s="23" t="inlineStr">
-        <is>
-          <t>4.14 kg</t>
-        </is>
-      </c>
-      <c r="BO50" s="23" t="inlineStr">
-        <is>
-          <t>4.14 kg</t>
-        </is>
-      </c>
-      <c r="BP50" s="23" t="inlineStr">
-        <is>
-          <t>42.5 x 35.7 x 20.2 cm</t>
-        </is>
-      </c>
-      <c r="BQ50" s="23" t="inlineStr">
-        <is>
-          <t>42.50 x 35.70 x 20.20 cm</t>
-        </is>
-      </c>
-      <c r="BR50" s="13" t="inlineStr">
-        <is>
-          <t>轻型标准大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B01LX6WOFS</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14" t="inlineStr">
-        <is>
-          <t>Ecozone</t>
-        </is>
-      </c>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>EcoZone Carpet Shampoo Solution, Deep Cleans Upholstery, Manual &amp; Machine Cleaning, Fresh Cotton Scent, 3-in-1 Plant Based St</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B01LX6WOFS</t>
-        </is>
-      </c>
-      <c r="M51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen:Kitchen &amp; Home Appliances:Vacuums &amp; Floor Care:Carpet Washers</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="O51" s="15">
-        <v>35994</v>
-      </c>
-      <c r="P51" s="15">
-        <v>-5051</v>
-      </c>
-      <c r="Q51" s="16">
-        <v>-0.16</v>
-      </c>
-      <c r="R51" s="17" t="inlineStr">
-        <is>
-          <t>Carpet Washers</t>
-        </is>
-      </c>
-      <c r="S51" s="18" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="T51" s="15">
-        <v>186</v>
-      </c>
-      <c r="U51" s="16">
-        <v>-0.08</v>
-      </c>
-      <c r="V51" s="15">
-        <v>1585</v>
-      </c>
-      <c r="W51" s="15" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X51" s="15">
-        <v>831</v>
-      </c>
-      <c r="Y51" s="19">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="20">
-        <v>8.52</v>
-      </c>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51" s="2">
-        <v>9</v>
-      </c>
-      <c r="AD51" s="19">
-        <v>906</v>
-      </c>
-      <c r="AE51" s="15">
-        <v>2</v>
-      </c>
-      <c r="AF51" s="21">
-        <v>4.4</v>
-      </c>
-      <c r="AG51" s="22">
-        <v>0.0108</v>
-      </c>
-      <c r="AH51" s="20">
-        <v>3.1</v>
-      </c>
-      <c r="AI51" s="16">
-        <v>0.64</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="13" t="inlineStr">
-        <is>
-          <t>2017-05-30</t>
-        </is>
-      </c>
-      <c r="AL51" s="19">
-        <v>3417</v>
-      </c>
-      <c r="AM51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="19">
-        <v>10</v>
-      </c>
-      <c r="AR51" s="19">
-        <v>3</v>
-      </c>
-      <c r="AS51" s="14" t="inlineStr">
-        <is>
-          <t>Siwa Salt Direct</t>
-        </is>
-      </c>
-      <c r="AT51" s="13" t="inlineStr">
-        <is>
-          <t>FBA</t>
-        </is>
-      </c>
-      <c r="AU51" s="13" t="inlineStr">
-        <is>
-          <t>GB</t>
-        </is>
-      </c>
-      <c r="AV51" s="14" t="inlineStr">
-        <is>
-          <t>Enfield Middlesex EN2 7LL GB</t>
-        </is>
-      </c>
-      <c r="AW51" s="13" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1DDI4YT9F1YO7</t>
-        </is>
-      </c>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD51" s="13" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51" s="23" t="inlineStr">
+      <c r="BI49" s="23" t="inlineStr">
         <is>
           <t>Amazon's Choice</t>
         </is>
       </c>
-      <c r="BJ51" s="23" t="inlineStr">
+      <c r="BJ49" s="23" t="inlineStr">
         <is>
           <t>0.43 g</t>
         </is>
       </c>
-      <c r="BK51" s="23" t="inlineStr">
+      <c r="BK49" s="23" t="inlineStr">
         <is>
           <t>0.43 g</t>
         </is>
       </c>
-      <c r="BL51" s="23" t="inlineStr">
+      <c r="BL49" s="23" t="inlineStr">
         <is>
           <t>8 x 12 x 25 cm</t>
         </is>
       </c>
-      <c r="BM51" s="23" t="inlineStr">
+      <c r="BM49" s="23" t="inlineStr">
         <is>
           <t>8.00 x 12.00 x 25.00 cm</t>
         </is>
       </c>
-      <c r="BN51" s="23" t="inlineStr">
+      <c r="BN49" s="23" t="inlineStr">
         <is>
           <t>1.06 kg</t>
         </is>
       </c>
-      <c r="BO51" s="23" t="inlineStr">
+      <c r="BO49" s="23" t="inlineStr">
         <is>
           <t>1.06 kg</t>
         </is>
       </c>
-      <c r="BP51" s="23" t="inlineStr">
+      <c r="BP49" s="23" t="inlineStr">
         <is>
           <t>23.4 x 11.9 x 7 cm</t>
         </is>
       </c>
-      <c r="BQ51" s="23" t="inlineStr">
+      <c r="BQ49" s="23" t="inlineStr">
         <is>
           <t>23.40 x 11.90 x 7.00 cm</t>
         </is>
       </c>
-      <c r="BR51" s="13" t="inlineStr">
+      <c r="BR49" s="13" t="inlineStr">
         <is>
           <t>小包裹</t>
         </is>
@@ -19076,188 +18522,173 @@
     <hyperlink ref="L27" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0HC7H41NZ"/>
     <hyperlink ref="M27" r:id="rId187" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N27" r:id="rId188"/>
-    <hyperlink ref="C28" r:id="rId189" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
-    <hyperlink ref="G28" r:id="rId190" tooltip="https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0FNX6YLCJ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J28" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1"/>
-    <hyperlink ref="K28" r:id="rId192" tooltip="https://images-na.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_US600_.jpg"/>
-    <hyperlink ref="L28" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
+    <hyperlink ref="C28" r:id="rId189" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
+    <hyperlink ref="G28" r:id="rId190" tooltip="https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB1CT2G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J28" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1"/>
+    <hyperlink ref="K28" r:id="rId192" tooltip="https://images-na.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_US600_.jpg"/>
+    <hyperlink ref="L28" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
     <hyperlink ref="M28" r:id="rId194" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N28" r:id="rId195"/>
-    <hyperlink ref="C29" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
-    <hyperlink ref="G29" r:id="rId197" tooltip="https://www.amazon.co.uk/stores/Olvy/page/42DFC99A-3581-46D9-A283-1EF2C68CD7B1?lp_asin=B0GGB1CT2G&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J29" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1"/>
-    <hyperlink ref="K29" r:id="rId199" tooltip="https://images-na.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_US600_.jpg"/>
-    <hyperlink ref="L29" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
-    <hyperlink ref="M29" r:id="rId201" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N29" r:id="rId202"/>
-    <hyperlink ref="AW29" r:id="rId203" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
-    <hyperlink ref="C30" r:id="rId204" tooltip="https://www.amazon.co.uk/dp/B00S9ORHDW"/>
-    <hyperlink ref="G30" r:id="rId205" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B00S9ORHDW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J30" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B00S9ORHDW?psc=1"/>
-    <hyperlink ref="K30" r:id="rId207" tooltip="https://images-na.ssl-images-amazon.com/images/I/618YXP+nVcL._AC_US600_.jpg"/>
-    <hyperlink ref="L30" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B00S9ORHDW"/>
+    <hyperlink ref="AW28" r:id="rId196" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A7NHEBYLM424G"/>
+    <hyperlink ref="C29" r:id="rId197" tooltip="https://www.amazon.co.uk/dp/B00S9ORHDW"/>
+    <hyperlink ref="G29" r:id="rId198" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B00S9ORHDW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J29" r:id="rId199" tooltip="https://www.amazon.co.uk/dp/B00S9ORHDW?psc=1"/>
+    <hyperlink ref="K29" r:id="rId200" tooltip="https://images-na.ssl-images-amazon.com/images/I/618YXP+nVcL._AC_US600_.jpg"/>
+    <hyperlink ref="L29" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B00S9ORHDW"/>
+    <hyperlink ref="M29" r:id="rId202" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N29" r:id="rId203"/>
+    <hyperlink ref="C30" r:id="rId204" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
+    <hyperlink ref="G30" r:id="rId205" tooltip="https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0DD49XPMY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J30" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1"/>
+    <hyperlink ref="K30" r:id="rId207" tooltip="https://images-na.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_US600_.jpg"/>
+    <hyperlink ref="L30" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
     <hyperlink ref="M30" r:id="rId209" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N30" r:id="rId210"/>
-    <hyperlink ref="C31" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
-    <hyperlink ref="G31" r:id="rId212" tooltip="https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0DD49XPMY&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J31" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1"/>
-    <hyperlink ref="K31" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_US600_.jpg"/>
-    <hyperlink ref="L31" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
+    <hyperlink ref="C31" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
+    <hyperlink ref="G31" r:id="rId212" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh"/>
+    <hyperlink ref="J31" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1"/>
+    <hyperlink ref="K31" r:id="rId214" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg"/>
+    <hyperlink ref="L31" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
     <hyperlink ref="M31" r:id="rId216" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N31" r:id="rId217"/>
-    <hyperlink ref="C32" r:id="rId218" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
-    <hyperlink ref="G32" r:id="rId219" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Hjh"/>
-    <hyperlink ref="J32" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1"/>
-    <hyperlink ref="K32" r:id="rId221" tooltip="https://images-na.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_US600_.jpg"/>
-    <hyperlink ref="L32" r:id="rId222" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
-    <hyperlink ref="M32" r:id="rId223" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N32" r:id="rId224"/>
-    <hyperlink ref="AW32" r:id="rId225" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH"/>
-    <hyperlink ref="C33" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
-    <hyperlink ref="G33" r:id="rId227" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0D6RSDL6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J33" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1"/>
-    <hyperlink ref="K33" r:id="rId229" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_US600_.jpg"/>
-    <hyperlink ref="L33" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
+    <hyperlink ref="AW31" r:id="rId218" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2UO155PK9MELH"/>
+    <hyperlink ref="C32" r:id="rId219" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
+    <hyperlink ref="G32" r:id="rId220" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0D6RSDL6X&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J32" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1"/>
+    <hyperlink ref="K32" r:id="rId222" tooltip="https://images-na.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_US600_.jpg"/>
+    <hyperlink ref="L32" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
+    <hyperlink ref="M32" r:id="rId224" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N32" r:id="rId225"/>
+    <hyperlink ref="C33" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
+    <hyperlink ref="G33" r:id="rId227" tooltip="https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J33" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y?psc=1"/>
+    <hyperlink ref="K33" r:id="rId229" tooltip="https://m.media-amazon.com/images/I/41z1m5EzSeL._AC_US600_.jpg"/>
+    <hyperlink ref="L33" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
     <hyperlink ref="M33" r:id="rId231" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N33" r:id="rId232"/>
-    <hyperlink ref="C34" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
-    <hyperlink ref="G34" r:id="rId234" tooltip="https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B00T31O22Y&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J34" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y?psc=1"/>
-    <hyperlink ref="K34" r:id="rId236" tooltip="https://m.media-amazon.com/images/I/41z1m5EzSeL._AC_US600_.jpg"/>
-    <hyperlink ref="L34" r:id="rId237" tooltip="https://www.amazon.co.uk/dp/B00T31O22Y"/>
+    <hyperlink ref="C34" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="G34" r:id="rId234" tooltip="https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J34" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
+    <hyperlink ref="K34" r:id="rId236" tooltip="https://images-na.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_US600_.jpg"/>
+    <hyperlink ref="L34" r:id="rId237" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
     <hyperlink ref="M34" r:id="rId238" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N34" r:id="rId239"/>
-    <hyperlink ref="C35" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
-    <hyperlink ref="G35" r:id="rId241" tooltip="https://www.amazon.co.uk/stores/Beldray/page/8BB71969-8E70-4472-AD09-CEB0284CA329?lp_asin=B0F2J9921T&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J35" r:id="rId242" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
-    <hyperlink ref="K35" r:id="rId243" tooltip="https://images-na.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_US600_.jpg"/>
-    <hyperlink ref="L35" r:id="rId244" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
-    <hyperlink ref="M35" r:id="rId245" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N35" r:id="rId246"/>
-    <hyperlink ref="AW35" r:id="rId247" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W"/>
-    <hyperlink ref="C36" r:id="rId248" tooltip="https://www.amazon.co.uk/dp/B0HJ8J22N9"/>
-    <hyperlink ref="G36" r:id="rId249" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0HJ8J22N9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J36" r:id="rId250" tooltip="https://www.amazon.co.uk/dp/B0HJ8J22N9?psc=1"/>
-    <hyperlink ref="K36" r:id="rId251" tooltip="https://m.media-amazon.com/images/I/41CYhsHx-oL._AC_US600_.jpg"/>
-    <hyperlink ref="L36" r:id="rId252" tooltip="https://www.amazon.co.uk/dp/B0HJ8J22N9"/>
-    <hyperlink ref="M36" r:id="rId253" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N36" r:id="rId254"/>
-    <hyperlink ref="AW36" r:id="rId255" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
-    <hyperlink ref="C37" r:id="rId256" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
-    <hyperlink ref="G37" r:id="rId257" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FP2ZHPNR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId258" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1"/>
-    <hyperlink ref="K37" r:id="rId259" tooltip="https://m.media-amazon.com/images/I/41gGVJL+XcL._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId260" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
+    <hyperlink ref="AW34" r:id="rId240" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2X5QKTIJPT88W"/>
+    <hyperlink ref="C35" r:id="rId241" tooltip="https://www.amazon.co.uk/dp/B0HJ8J22N9"/>
+    <hyperlink ref="G35" r:id="rId242" tooltip="https://www.amazon.co.uk/stores/VonHaus/page/E5359515-7CEA-400F-8537-AE2CBF4FE512?lp_asin=B0HJ8J22N9&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J35" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0HJ8J22N9?psc=1"/>
+    <hyperlink ref="K35" r:id="rId244" tooltip="https://m.media-amazon.com/images/I/41CYhsHx-oL._AC_US600_.jpg"/>
+    <hyperlink ref="L35" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0HJ8J22N9"/>
+    <hyperlink ref="M35" r:id="rId246" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N35" r:id="rId247"/>
+    <hyperlink ref="AW35" r:id="rId248" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1AFJESMA8SCN6"/>
+    <hyperlink ref="C36" r:id="rId249" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
+    <hyperlink ref="G36" r:id="rId250" tooltip="https://www.amazon.co.uk/stores/K%C3%A4rcherUK/page/F6053778-BFEE-41CB-9B1B-A16ECF7857D7?lp_asin=B0FP2ZHPNR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J36" r:id="rId251" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1"/>
+    <hyperlink ref="K36" r:id="rId252" tooltip="https://m.media-amazon.com/images/I/41gGVJL+XcL._AC_US600_.jpg"/>
+    <hyperlink ref="L36" r:id="rId253" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
+    <hyperlink ref="M36" r:id="rId254" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N36" r:id="rId255"/>
+    <hyperlink ref="C37" r:id="rId256" tooltip="https://www.amazon.co.uk/dp/B0GL3ZR1JF"/>
+    <hyperlink ref="G37" r:id="rId257" tooltip="https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0GL3ZR1JF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId258" tooltip="https://www.amazon.co.uk/dp/B0GL3ZR1JF?psc=1"/>
+    <hyperlink ref="K37" r:id="rId259" tooltip="https://images-na.ssl-images-amazon.com/images/I/71j+wRZ7ZaL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId260" tooltip="https://www.amazon.co.uk/dp/B0GL3ZR1JF"/>
     <hyperlink ref="M37" r:id="rId261" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N37" r:id="rId262"/>
-    <hyperlink ref="C38" r:id="rId263" tooltip="https://www.amazon.co.uk/dp/B0GL3ZR1JF"/>
-    <hyperlink ref="G38" r:id="rId264" tooltip="https://www.amazon.co.uk/stores/SharkINinja/page/525766F4-D5DD-4FFC-8A20-92AC184FF87C?lp_asin=B0GL3ZR1JF&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId265" tooltip="https://www.amazon.co.uk/dp/B0GL3ZR1JF?psc=1"/>
-    <hyperlink ref="K38" r:id="rId266" tooltip="https://images-na.ssl-images-amazon.com/images/I/71j+wRZ7ZaL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId267" tooltip="https://www.amazon.co.uk/dp/B0GL3ZR1JF"/>
+    <hyperlink ref="C38" r:id="rId263" tooltip="https://www.amazon.co.uk/dp/B0DPGJG95L"/>
+    <hyperlink ref="G38" r:id="rId264" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0DPGJG95L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId265" tooltip="https://www.amazon.co.uk/dp/B0DPGJG95L?psc=1"/>
+    <hyperlink ref="K38" r:id="rId266" tooltip="https://m.media-amazon.com/images/I/31NW4G31THL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId267" tooltip="https://www.amazon.co.uk/dp/B0DPGJG95L"/>
     <hyperlink ref="M38" r:id="rId268" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N38" r:id="rId269"/>
-    <hyperlink ref="C39" r:id="rId270" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="G39" r:id="rId271" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0753NXDPR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId272" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K39" r:id="rId273" tooltip="https://m.media-amazon.com/images/I/31LC0CHQzZL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId274" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="M39" r:id="rId275" tooltip="https://www.amazon.co.uk/b?node=471450031"/>
+    <hyperlink ref="C39" r:id="rId270" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="G39" r:id="rId271" tooltip="https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId272" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
+    <hyperlink ref="K39" r:id="rId273" tooltip="https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId274" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="M39" r:id="rId275" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N39" r:id="rId276"/>
-    <hyperlink ref="AW39" r:id="rId277" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AKGAA3WULFPOP"/>
-    <hyperlink ref="C40" r:id="rId278" tooltip="https://www.amazon.co.uk/dp/B0DPGJG95L"/>
-    <hyperlink ref="G40" r:id="rId279" tooltip="https://www.amazon.co.uk/stores/BISSELL/page/F19BE08B-0A2F-4932-9CC7-F2B7E50EE7FF?lp_asin=B0DPGJG95L&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId280" tooltip="https://www.amazon.co.uk/dp/B0DPGJG95L?psc=1"/>
-    <hyperlink ref="K40" r:id="rId281" tooltip="https://m.media-amazon.com/images/I/31NW4G31THL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId282" tooltip="https://www.amazon.co.uk/dp/B0DPGJG95L"/>
-    <hyperlink ref="M40" r:id="rId283" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N40" r:id="rId284"/>
-    <hyperlink ref="C41" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
-    <hyperlink ref="G41" r:id="rId286" tooltip="https://www.amazon.co.uk/stores/SwanProductsLtd/page/69D73DEE-49FE-4AEE-B38D-1948D70187CB?lp_asin=B0B4JST7J8&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J41" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
-    <hyperlink ref="K41" r:id="rId288" tooltip="https://images-na.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId289" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="C40" r:id="rId277" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="G40" r:id="rId278" tooltip="https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J40" r:id="rId279" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
+    <hyperlink ref="K40" r:id="rId280" tooltip="https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId281" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="M40" r:id="rId282" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N40" r:id="rId283"/>
+    <hyperlink ref="AW40" r:id="rId284" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ"/>
+    <hyperlink ref="C41" r:id="rId285" tooltip="https://www.amazon.co.uk/dp/B0HGKV75WF"/>
+    <hyperlink ref="G41" r:id="rId286" tooltip="https://www.amazon.co.uk/stores/WelcometoJuibaoHomeLife/page/59D05DFD-B4BC-4B79-9C37-39738D5979A4?lp_asin=B0HGKV75WF&amp;ref_=ast_bln"/>
+    <hyperlink ref="J41" r:id="rId287" tooltip="https://www.amazon.co.uk/dp/B0HGKV75WF?psc=1"/>
+    <hyperlink ref="K41" r:id="rId288" tooltip="https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId289" tooltip="https://www.amazon.co.uk/dp/B0HGKV75WF"/>
     <hyperlink ref="M41" r:id="rId290" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N41" r:id="rId291"/>
-    <hyperlink ref="C42" r:id="rId292" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
-    <hyperlink ref="G42" r:id="rId293" tooltip="https://www.amazon.co.uk/stores/Daewoo/page/F8BDC7B4-3E6A-4593-ABD8-5A8336047C2A?lp_asin=B0CZRYCLNT&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J42" r:id="rId294" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
-    <hyperlink ref="K42" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId296" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
-    <hyperlink ref="M42" r:id="rId297" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N42" r:id="rId298"/>
-    <hyperlink ref="AW42" r:id="rId299" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A24NGU5R55LIUJ"/>
-    <hyperlink ref="C43" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B0HGKV75WF"/>
-    <hyperlink ref="G43" r:id="rId301" tooltip="https://www.amazon.co.uk/stores/WelcometoJuibaoHomeLife/page/59D05DFD-B4BC-4B79-9C37-39738D5979A4?lp_asin=B0HGKV75WF&amp;ref_=ast_bln"/>
-    <hyperlink ref="J43" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B0HGKV75WF?psc=1"/>
-    <hyperlink ref="K43" r:id="rId303" tooltip="https://m.media-amazon.com/images/I/412FDqPMD9L._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId304" tooltip="https://www.amazon.co.uk/dp/B0HGKV75WF"/>
+    <hyperlink ref="AW41" r:id="rId292" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
+    <hyperlink ref="C42" r:id="rId293" tooltip="https://www.amazon.co.uk/dp/B0H4RJFHM6"/>
+    <hyperlink ref="G42" r:id="rId294" tooltip="https://www.amazon.co.uknull"/>
+    <hyperlink ref="J42" r:id="rId295" tooltip="https://www.amazon.co.uk/dp/B0H4RJFHM6?psc=1"/>
+    <hyperlink ref="K42" r:id="rId296" tooltip="https://images-na.ssl-images-amazon.com/images/I/71sct2oNe0L._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId297" tooltip="https://www.amazon.co.uk/dp/B0H4RJFHM6"/>
+    <hyperlink ref="M42" r:id="rId298" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N42" r:id="rId299"/>
+    <hyperlink ref="C43" r:id="rId300" tooltip="https://www.amazon.co.uk/dp/B081427M5C"/>
+    <hyperlink ref="G43" r:id="rId301" tooltip="https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B081427M5C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J43" r:id="rId302" tooltip="https://www.amazon.co.uk/dp/B081427M5C?psc=1"/>
+    <hyperlink ref="K43" r:id="rId303" tooltip="https://m.media-amazon.com/images/I/51l75+jHxUL._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId304" tooltip="https://www.amazon.co.uk/dp/B081427M5C"/>
     <hyperlink ref="M43" r:id="rId305" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N43" r:id="rId306"/>
-    <hyperlink ref="AW43" r:id="rId307" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A190HADBP97HLJ"/>
-    <hyperlink ref="C44" r:id="rId308" tooltip="https://www.amazon.co.uk/dp/B0H4RJFHM6"/>
-    <hyperlink ref="G44" r:id="rId309" tooltip="https://www.amazon.co.uknull"/>
-    <hyperlink ref="J44" r:id="rId310" tooltip="https://www.amazon.co.uk/dp/B0H4RJFHM6?psc=1"/>
-    <hyperlink ref="K44" r:id="rId311" tooltip="https://images-na.ssl-images-amazon.com/images/I/71sct2oNe0L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId312" tooltip="https://www.amazon.co.uk/dp/B0H4RJFHM6"/>
-    <hyperlink ref="M44" r:id="rId313" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N44" r:id="rId314"/>
-    <hyperlink ref="C45" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B081427M5C"/>
-    <hyperlink ref="G45" r:id="rId316" tooltip="https://www.amazon.co.uk/stores/RugDoctor/page/8161ECDA-1080-4AC4-92F6-141201B689F6?lp_asin=B081427M5C&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B081427M5C?psc=1"/>
-    <hyperlink ref="K45" r:id="rId318" tooltip="https://m.media-amazon.com/images/I/51l75+jHxUL._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B081427M5C"/>
+    <hyperlink ref="C44" r:id="rId307" tooltip="https://www.amazon.co.uk/dp/B0HC3856PH"/>
+    <hyperlink ref="G44" r:id="rId308" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gloppers"/>
+    <hyperlink ref="J44" r:id="rId309" tooltip="https://www.amazon.co.uk/dp/B0HC3856PH?psc=1"/>
+    <hyperlink ref="K44" r:id="rId310" tooltip="https://images-na.ssl-images-amazon.com/images/I/61O26S3eC8L._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId311" tooltip="https://www.amazon.co.uk/dp/B0HC3856PH"/>
+    <hyperlink ref="M44" r:id="rId312" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N44" r:id="rId313"/>
+    <hyperlink ref="AW44" r:id="rId314" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9YABL1QACO9J"/>
+    <hyperlink ref="C45" r:id="rId315" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
+    <hyperlink ref="G45" r:id="rId316" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId317" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57?psc=1"/>
+    <hyperlink ref="K45" r:id="rId318" tooltip="https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId319" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
     <hyperlink ref="M45" r:id="rId320" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N45" r:id="rId321"/>
-    <hyperlink ref="C46" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0HC3856PH"/>
-    <hyperlink ref="G46" r:id="rId323" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Gloppers"/>
-    <hyperlink ref="J46" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0HC3856PH?psc=1"/>
-    <hyperlink ref="K46" r:id="rId325" tooltip="https://images-na.ssl-images-amazon.com/images/I/61O26S3eC8L._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0HC3856PH"/>
+    <hyperlink ref="C46" r:id="rId322" tooltip="https://www.amazon.co.uk/dp/B0FM3VJXKQ"/>
+    <hyperlink ref="G46" r:id="rId323" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
+    <hyperlink ref="J46" r:id="rId324" tooltip="https://www.amazon.co.uk/dp/B0FM3VJXKQ?psc=1"/>
+    <hyperlink ref="K46" r:id="rId325" tooltip="https://m.media-amazon.com/images/I/41nOwlawyOL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId326" tooltip="https://www.amazon.co.uk/dp/B0FM3VJXKQ"/>
     <hyperlink ref="M46" r:id="rId327" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N46" r:id="rId328"/>
-    <hyperlink ref="AW46" r:id="rId329" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A9YABL1QACO9J"/>
-    <hyperlink ref="C47" r:id="rId330" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
-    <hyperlink ref="G47" r:id="rId331" tooltip="https://www.amazon.co.uk/stores/Tower/page/B9BC31B3-F435-465D-8067-69F67674D770?lp_asin=B09JSVWX57&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId332" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57?psc=1"/>
-    <hyperlink ref="K47" r:id="rId333" tooltip="https://m.media-amazon.com/images/I/41uf-z8AXOL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId334" tooltip="https://www.amazon.co.uk/dp/B09JSVWX57"/>
+    <hyperlink ref="AW46" r:id="rId329" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
+    <hyperlink ref="C47" r:id="rId330" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
+    <hyperlink ref="G47" r:id="rId331" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome"/>
+    <hyperlink ref="J47" r:id="rId332" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1"/>
+    <hyperlink ref="K47" r:id="rId333" tooltip="https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg"/>
+    <hyperlink ref="L47" r:id="rId334" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
     <hyperlink ref="M47" r:id="rId335" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
     <hyperlink ref="N47" r:id="rId336"/>
-    <hyperlink ref="C48" r:id="rId337" tooltip="https://www.amazon.co.uk/dp/B0FM3VJXKQ"/>
-    <hyperlink ref="G48" r:id="rId338" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=Vlihapy"/>
-    <hyperlink ref="J48" r:id="rId339" tooltip="https://www.amazon.co.uk/dp/B0FM3VJXKQ?psc=1"/>
-    <hyperlink ref="K48" r:id="rId340" tooltip="https://m.media-amazon.com/images/I/41nOwlawyOL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId341" tooltip="https://www.amazon.co.uk/dp/B0FM3VJXKQ"/>
-    <hyperlink ref="M48" r:id="rId342" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N48" r:id="rId343"/>
-    <hyperlink ref="AW48" r:id="rId344" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KUVQEB99D827"/>
-    <hyperlink ref="C49" r:id="rId345" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
-    <hyperlink ref="G49" r:id="rId346" tooltip="https://www.amazon.co.uk/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-uk&amp;field-keywords=VickyHome"/>
-    <hyperlink ref="J49" r:id="rId347" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1"/>
-    <hyperlink ref="K49" r:id="rId348" tooltip="https://m.media-amazon.com/images/I/41G0usLZmPL._AC_US600_.jpg"/>
-    <hyperlink ref="L49" r:id="rId349" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
-    <hyperlink ref="M49" r:id="rId350" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N49" r:id="rId351"/>
-    <hyperlink ref="AW49" r:id="rId352" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U"/>
-    <hyperlink ref="C50" r:id="rId353" tooltip="https://www.amazon.co.uk/dp/B0H8NPR9ZW"/>
-    <hyperlink ref="G50" r:id="rId354" tooltip="https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8NPR9ZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J50" r:id="rId355" tooltip="https://www.amazon.co.uk/dp/B0H8NPR9ZW?psc=1"/>
-    <hyperlink ref="K50" r:id="rId356" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wZpLFoJpL._AC_US600_.jpg"/>
-    <hyperlink ref="L50" r:id="rId357" tooltip="https://www.amazon.co.uk/dp/B0H8NPR9ZW"/>
-    <hyperlink ref="M50" r:id="rId358" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N50" r:id="rId359"/>
-    <hyperlink ref="AW50" r:id="rId360" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL"/>
-    <hyperlink ref="C51" r:id="rId361" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
-    <hyperlink ref="G51" r:id="rId362" tooltip="https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J51" r:id="rId363" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1"/>
-    <hyperlink ref="K51" r:id="rId364" tooltip="https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg"/>
-    <hyperlink ref="L51" r:id="rId365" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
-    <hyperlink ref="M51" r:id="rId366" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
-    <hyperlink ref="N51" r:id="rId367"/>
-    <hyperlink ref="AW51" r:id="rId368" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1DDI4YT9F1YO7"/>
+    <hyperlink ref="AW47" r:id="rId337" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AJD9ONY8MI53U"/>
+    <hyperlink ref="C48" r:id="rId338" tooltip="https://www.amazon.co.uk/dp/B0H8NPR9ZW"/>
+    <hyperlink ref="G48" r:id="rId339" tooltip="https://www.amazon.co.uk/stores/24-hourrapidresponse/page/2AA9E9E0-E703-4ECF-AC64-366A67AE77A7?lp_asin=B0H8NPR9ZW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J48" r:id="rId340" tooltip="https://www.amazon.co.uk/dp/B0H8NPR9ZW?psc=1"/>
+    <hyperlink ref="K48" r:id="rId341" tooltip="https://images-na.ssl-images-amazon.com/images/I/71wZpLFoJpL._AC_US600_.jpg"/>
+    <hyperlink ref="L48" r:id="rId342" tooltip="https://www.amazon.co.uk/dp/B0H8NPR9ZW"/>
+    <hyperlink ref="M48" r:id="rId343" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N48" r:id="rId344"/>
+    <hyperlink ref="AW48" r:id="rId345" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ABDQMGK4MGMOL"/>
+    <hyperlink ref="C49" r:id="rId346" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
+    <hyperlink ref="G49" r:id="rId347" tooltip="https://www.amazon.co.uk/stores/Ecozone/page/B457F3C7-F7E8-45B1-B9BB-D317BE4CAE57?lp_asin=B01LX6WOFS&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J49" r:id="rId348" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS?psc=1"/>
+    <hyperlink ref="K49" r:id="rId349" tooltip="https://images-na.ssl-images-amazon.com/images/I/61toYqbNVBL._AC_US600_.jpg"/>
+    <hyperlink ref="L49" r:id="rId350" tooltip="https://www.amazon.co.uk/dp/B01LX6WOFS"/>
+    <hyperlink ref="M49" r:id="rId351" tooltip="https://www.amazon.co.uk/b?node=3147751"/>
+    <hyperlink ref="N49" r:id="rId352"/>
+    <hyperlink ref="AW49" r:id="rId353" tooltip="https://www.amazon.co.uk/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1DDI4YT9F1YO7"/>
   </hyperlinks>
-  <drawing r:id="rId369"/>
+  <drawing r:id="rId354"/>
 </worksheet>
 </file>
 
@@ -19327,7 +18758,7 @@
         <v>105.36101141924959</v>
       </c>
       <c r="G2" s="22">
-        <v>0.4899949375183182</v>
+        <v>0.5257590485447996</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19337,18 +18768,18 @@
         </is>
       </c>
       <c r="B3" s="15">
-        <v>6029</v>
+        <v>4525</v>
       </c>
       <c r="C3" s="15">
-        <v>696729</v>
+        <v>666664</v>
       </c>
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
       <c r="F3" s="20">
-        <v>115.56294576214961</v>
+        <v>147.32906077348068</v>
       </c>
       <c r="G3" s="22">
-        <v>0.16064053715595109</v>
+        <v>0.12936703070501457</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19358,18 +18789,18 @@
         </is>
       </c>
       <c r="B4" s="15">
-        <v>4742</v>
+        <v>3693</v>
       </c>
       <c r="C4" s="15">
-        <v>359960</v>
+        <v>349785</v>
       </c>
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
       <c r="F4" s="20">
-        <v>75.90889919865036</v>
+        <v>94.71567831031682</v>
       </c>
       <c r="G4" s="22">
-        <v>0.126348884921798</v>
+        <v>0.1055806506947224</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19390,7 +18821,7 @@
         <v>190.1425</v>
       </c>
       <c r="G5" s="22">
-        <v>0.02131571234446191</v>
+        <v>0.02287151924066556</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19411,7 +18842,7 @@
         <v>49.99015219337511</v>
       </c>
       <c r="G6" s="22">
-        <v>0.05952412672190989</v>
+        <v>0.06386871747955858</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19432,7 +18863,7 @@
         <v>54.020207852194</v>
       </c>
       <c r="G7" s="22">
-        <v>0.046148517225760036</v>
+        <v>0.04951683915604094</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19453,7 +18884,7 @@
         <v>59.989830508474576</v>
       </c>
       <c r="G8" s="22">
-        <v>0.02358050678106099</v>
+        <v>0.025301618159986276</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19474,7 +18905,7 @@
         <v>67.99026763990268</v>
       </c>
       <c r="G9" s="22">
-        <v>0.010950947216967308</v>
+        <v>0.011750243009891932</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19495,7 +18926,7 @@
         <v>59.99002493765586</v>
       </c>
       <c r="G10" s="22">
-        <v>0.010684500812661533</v>
+        <v>0.011464349019383613</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19516,7 +18947,7 @@
         <v>54.9889705882353</v>
       </c>
       <c r="G11" s="22">
-        <v>0.00724734219711705</v>
+        <v>0.0077763165418262906</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19537,7 +18968,7 @@
         <v>54.99159663865546</v>
       </c>
       <c r="G12" s="22">
-        <v>0.0063414244224774185</v>
+        <v>0.006804276974098004</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19558,7 +18989,7 @@
         <v>59.99078341013825</v>
       </c>
       <c r="G13" s="22">
-        <v>0.005781886973435293</v>
+        <v>0.006203899594030534</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19579,7 +19010,7 @@
         <v>39.99074074074074</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0057552423330047165</v>
+        <v>0.0061753101949797015</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19600,7 +19031,7 @@
         <v>47.96045197740113</v>
       </c>
       <c r="G15" s="22">
-        <v>0.004716101356212198</v>
+        <v>0.005060323631997255</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19621,7 +19052,7 @@
         <v>66.0</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0026378194026271617</v>
+        <v>0.0028303505060323633</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19642,7 +19073,7 @@
         <v>113.05454545454545</v>
       </c>
       <c r="G17" s="22">
-        <v>0.0014654552236817563</v>
+        <v>0.0015724169477957573</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19663,7 +19094,7 @@
         <v>62.98765432098765</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0021582158748767685</v>
+        <v>0.002315741323117388</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19684,7 +19115,7 @@
         <v>49.990196078431374</v>
       </c>
       <c r="G19" s="22">
-        <v>0.0027177533239188937</v>
+        <v>0.002916118703184859</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19705,7 +19136,7 @@
         <v>34.58119658119658</v>
       </c>
       <c r="G20" s="22">
-        <v>0.0031174229303775544</v>
+        <v>0.003344959688947338</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19726,7 +19157,7 @@
         <v>35.57281553398058</v>
       </c>
       <c r="G21" s="22">
-        <v>0.002744397964349471</v>
+        <v>0.002944708102235691</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19747,7 +19178,7 @@
         <v>60.0</v>
       </c>
       <c r="G22" s="22">
-        <v>0.0011723641789454051</v>
+        <v>0.001257933558236606</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19768,7 +19199,7 @@
         <v>8.521505376344086</v>
       </c>
       <c r="G23" s="22">
-        <v>0.004955903120087394</v>
+        <v>0.005317628223454743</v>
       </c>
     </row>
   </sheetData>
@@ -19779,7 +19210,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -19832,18 +19263,18 @@
         </is>
       </c>
       <c r="B2" s="15">
-        <v>26365</v>
+        <v>24861</v>
       </c>
       <c r="C2" s="15">
-        <v>2482472</v>
+        <v>2452407</v>
       </c>
       <c r="D2" s="15"/>
       <c r="E2" s="15"/>
       <c r="F2" s="20">
-        <v>94.15786080030344</v>
+        <v>98.64474478098226</v>
       </c>
       <c r="G2" s="22">
-        <v>0.7024859449521729</v>
+        <v>0.7107610498027331</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19864,7 +19295,7 @@
         <v>198.99021207177813</v>
       </c>
       <c r="G3" s="22">
-        <v>0.04899949375183182</v>
+        <v>0.05257590485447996</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19885,7 +19316,7 @@
         <v>247.13020030816642</v>
       </c>
       <c r="G4" s="22">
-        <v>0.034584743278889454</v>
+        <v>0.03710903996797987</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19906,7 +19337,7 @@
         <v>49.99015219337511</v>
       </c>
       <c r="G5" s="22">
-        <v>0.05952412672190989</v>
+        <v>0.06386871747955858</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19927,7 +19358,7 @@
         <v>54.020207852194</v>
       </c>
       <c r="G6" s="22">
-        <v>0.046148517225760036</v>
+        <v>0.04951683915604094</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19948,7 +19379,7 @@
         <v>59.989830508474576</v>
       </c>
       <c r="G7" s="22">
-        <v>0.02358050678106099</v>
+        <v>0.025301618159986276</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19969,7 +19400,7 @@
         <v>67.99026763990268</v>
       </c>
       <c r="G8" s="22">
-        <v>0.010950947216967308</v>
+        <v>0.011750243009891932</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -19990,7 +19421,7 @@
         <v>59.99002493765586</v>
       </c>
       <c r="G9" s="22">
-        <v>0.010684500812661533</v>
+        <v>0.011464349019383613</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20011,7 +19442,7 @@
         <v>54.9889705882353</v>
       </c>
       <c r="G10" s="22">
-        <v>0.00724734219711705</v>
+        <v>0.0077763165418262906</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20032,175 +19463,154 @@
         <v>54.99159663865546</v>
       </c>
       <c r="G11" s="22">
-        <v>0.0063414244224774185</v>
+        <v>0.006804276974098004</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Reliapart</t>
+          <t>UK Direct 247</t>
         </is>
       </c>
       <c r="B12" s="15">
-        <v>1049</v>
+        <v>177</v>
       </c>
       <c r="C12" s="15">
-        <v>10175</v>
+        <v>8489</v>
       </c>
       <c r="D12" s="15"/>
       <c r="E12" s="15"/>
       <c r="F12" s="20">
-        <v>9.699714013346044</v>
+        <v>47.96045197740113</v>
       </c>
       <c r="G12" s="22">
-        <v>0.027950227811675683</v>
+        <v>0.005060323631997255</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>UK Direct 247</t>
+          <t>HEYWORK</t>
         </is>
       </c>
       <c r="B13" s="15">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="C13" s="15">
-        <v>8489</v>
+        <v>6534</v>
       </c>
       <c r="D13" s="15"/>
       <c r="E13" s="15"/>
       <c r="F13" s="20">
-        <v>47.96045197740113</v>
+        <v>66.0</v>
       </c>
       <c r="G13" s="22">
-        <v>0.004716101356212198</v>
+        <v>0.0028303505060323633</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>HEYWORK</t>
+          <t>PUXI Tech</t>
         </is>
       </c>
       <c r="B14" s="15">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="C14" s="15">
-        <v>6534</v>
+        <v>5102</v>
       </c>
       <c r="D14" s="15"/>
       <c r="E14" s="15"/>
       <c r="F14" s="20">
-        <v>66.0</v>
+        <v>62.98765432098765</v>
       </c>
       <c r="G14" s="22">
-        <v>0.0026378194026271617</v>
+        <v>0.002315741323117388</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>PUXI Tech</t>
+          <t>Treasuretool</t>
         </is>
       </c>
       <c r="B15" s="15">
-        <v>81</v>
+        <v>117</v>
       </c>
       <c r="C15" s="15">
-        <v>5102</v>
+        <v>4046</v>
       </c>
       <c r="D15" s="15"/>
       <c r="E15" s="15"/>
       <c r="F15" s="20">
-        <v>62.98765432098765</v>
+        <v>34.58119658119658</v>
       </c>
       <c r="G15" s="22">
-        <v>0.0021582158748767685</v>
+        <v>0.003344959688947338</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Treasuretool</t>
+          <t>Lucn</t>
         </is>
       </c>
       <c r="B16" s="15">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="C16" s="15">
-        <v>4046</v>
+        <v>3664</v>
       </c>
       <c r="D16" s="15"/>
       <c r="E16" s="15"/>
       <c r="F16" s="20">
-        <v>34.58119658119658</v>
+        <v>35.57281553398058</v>
       </c>
       <c r="G16" s="22">
-        <v>0.0031174229303775544</v>
+        <v>0.002944708102235691</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>Lucn</t>
+          <t>Xinhua County Hongxu Trading Co., Ltd</t>
         </is>
       </c>
       <c r="B17" s="15">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="C17" s="15">
-        <v>3664</v>
+        <v>2640</v>
       </c>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
       <c r="F17" s="20">
-        <v>35.57281553398058</v>
+        <v>60.0</v>
       </c>
       <c r="G17" s="22">
-        <v>0.002744397964349471</v>
+        <v>0.001257933558236606</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>Xinhua County Hongxu Trading Co., Ltd</t>
+          <t>Siwa Salt Direct</t>
         </is>
       </c>
       <c r="B18" s="15">
-        <v>44</v>
+        <v>186</v>
       </c>
       <c r="C18" s="15">
-        <v>2640</v>
+        <v>1585</v>
       </c>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="20">
-        <v>60.0</v>
+        <v>8.521505376344086</v>
       </c>
       <c r="G18" s="22">
-        <v>0.0011723641789454051</v>
-      </c>
-    </row>
-    <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Siwa Salt Direct</t>
-        </is>
-      </c>
-      <c r="B19" s="15">
-        <v>186</v>
-      </c>
-      <c r="C19" s="15">
-        <v>1585</v>
-      </c>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="20">
-        <v>8.521505376344086</v>
-      </c>
-      <c r="G19" s="22">
-        <v>0.004955903120087394</v>
+        <v>0.005317628223454743</v>
       </c>
     </row>
   </sheetData>
